--- a/data/Oct/InternalDailyReport_Oct.xlsx
+++ b/data/Oct/InternalDailyReport_Oct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE64E91-6610-407C-B341-2F5663DF8B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C046F6-7BC3-4544-A595-BD982D1D058E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="23" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="03-10" sheetId="26" r:id="rId4"/>
     <sheet name="05-10" sheetId="27" r:id="rId5"/>
     <sheet name="06-10" sheetId="28" r:id="rId6"/>
+    <sheet name="07-10" sheetId="29" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01-10'!$A$2:$P$53</definedName>
@@ -26,6 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03-10'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05-10'!$A$2:$P$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06-10'!$A$2:$P$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07-10'!$A$2:$P$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -68,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="903">
   <si>
     <t>NGÀY</t>
   </si>
@@ -2453,6 +2455,330 @@
   </si>
   <si>
     <t>grab</t>
+  </si>
+  <si>
+    <t>Tu Tu</t>
+  </si>
+  <si>
+    <t>HD064689</t>
+  </si>
+  <si>
+    <t>466/39 le van sy f 14</t>
+  </si>
+  <si>
+    <t>07-10-2026</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thuỳ Trang</t>
+  </si>
+  <si>
+    <t>HD064608</t>
+  </si>
+  <si>
+    <t>41A Huỳnh Tịnh của p19</t>
+  </si>
+  <si>
+    <t>Ngọc Ánh</t>
+  </si>
+  <si>
+    <t>HD064642</t>
+  </si>
+  <si>
+    <t>2/21 phan thúc duyện</t>
+  </si>
+  <si>
+    <t>BN6352</t>
+  </si>
+  <si>
+    <t>HD064708</t>
+  </si>
+  <si>
+    <t>Tú Oanh - fb Không Nói Xâm</t>
+  </si>
+  <si>
+    <t>HD064593</t>
+  </si>
+  <si>
+    <t>69 Dương Đình Nghệ P8</t>
+  </si>
+  <si>
+    <t>AT 07-10</t>
+  </si>
+  <si>
+    <t>Đinh Thị Thu Hà</t>
+  </si>
+  <si>
+    <t>HD064612</t>
+  </si>
+  <si>
+    <t>176/1 Nguyễn Văn Thương, P. Thạnh Mỹ Tây</t>
+  </si>
+  <si>
+    <t>HD064640</t>
+  </si>
+  <si>
+    <t>mỹ huyền</t>
+  </si>
+  <si>
+    <t>HD064774</t>
+  </si>
+  <si>
+    <t>hẻm 2581/27 ấp4 đường huỳnh tấn phát, xã phú xuân</t>
+  </si>
+  <si>
+    <t>Sang - fb Ivy Thụy Pham sale</t>
+  </si>
+  <si>
+    <t>HD064668</t>
+  </si>
+  <si>
+    <t>349/175 Lê Đại Hành Phường Phú Thọ</t>
+  </si>
+  <si>
+    <t>Doan Ngoc Anh Thu</t>
+  </si>
+  <si>
+    <t>HD064813</t>
+  </si>
+  <si>
+    <t>Chung cư homyland2, 307 Nguyễn duy trinh, bình trưng</t>
+  </si>
+  <si>
+    <t>Sea</t>
+  </si>
+  <si>
+    <t>HD064748</t>
+  </si>
+  <si>
+    <t>32/16a đường số 6, P. BHHA</t>
+  </si>
+  <si>
+    <t>Thu Ba DS</t>
+  </si>
+  <si>
+    <t>HD064675</t>
+  </si>
+  <si>
+    <t>395 Bùi Đình Tuý, p14</t>
+  </si>
+  <si>
+    <t>Nhi Nguyễn</t>
+  </si>
+  <si>
+    <t>HD064789</t>
+  </si>
+  <si>
+    <t>128 Hồng Hà, Phường 9</t>
+  </si>
+  <si>
+    <t>chị Thu Dương</t>
+  </si>
+  <si>
+    <t>HD064786</t>
+  </si>
+  <si>
+    <t>158 đào duy anh, P. đức nhuận</t>
+  </si>
+  <si>
+    <t>Linh Dịu Dàng</t>
+  </si>
+  <si>
+    <t>HD064810</t>
+  </si>
+  <si>
+    <t>362/22 lê đức thọ an nhơn</t>
+  </si>
+  <si>
+    <t>Kelly Phan</t>
+  </si>
+  <si>
+    <t>HD064673</t>
+  </si>
+  <si>
+    <t>240/6A lê thánh tôn bến thành</t>
+  </si>
+  <si>
+    <t>Huỳnh Anh</t>
+  </si>
+  <si>
+    <t>HD064778</t>
+  </si>
+  <si>
+    <t>Angelica Lumiere, Vinhome Grand Park, Phường long bình</t>
+  </si>
+  <si>
+    <t>Chip Chip</t>
+  </si>
+  <si>
+    <t>HD064771</t>
+  </si>
+  <si>
+    <t>71/16 thới an 16</t>
+  </si>
+  <si>
+    <t>Trần Thu Hường</t>
+  </si>
+  <si>
+    <t>HD064655</t>
+  </si>
+  <si>
+    <t>124/28 nguyễn văn cừ, p.cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Vũ Hồng Ly</t>
+  </si>
+  <si>
+    <t>HD064734</t>
+  </si>
+  <si>
+    <t>240/29, Hiệp Thành 13, P Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Cin Vo</t>
+  </si>
+  <si>
+    <t>HD064606</t>
+  </si>
+  <si>
+    <t>268 bà hom p14</t>
+  </si>
+  <si>
+    <t>Bông Bông</t>
+  </si>
+  <si>
+    <t>HD064666</t>
+  </si>
+  <si>
+    <t>Saicon riverside complex (block C1) Số 4 đào trí phú thuận</t>
+  </si>
+  <si>
+    <t>Thu Pham</t>
+  </si>
+  <si>
+    <t>HD064657</t>
+  </si>
+  <si>
+    <t>chung cư Terra Royal 280 nam kỳ khởi nghĩa, phường võ thị sáu</t>
+  </si>
+  <si>
+    <t>HD064688</t>
+  </si>
+  <si>
+    <t>sldraalvinaa_</t>
+  </si>
+  <si>
+    <t>HD064502</t>
+  </si>
+  <si>
+    <t>1 Đường Số 15 Villa 01 David, An Khánh</t>
+  </si>
+  <si>
+    <t>My My</t>
+  </si>
+  <si>
+    <t>HD064651</t>
+  </si>
+  <si>
+    <t>CC TOPAZ ELITE PHOENIX 1A</t>
+  </si>
+  <si>
+    <t>Trang Nguyen</t>
+  </si>
+  <si>
+    <t>HD064597</t>
+  </si>
+  <si>
+    <t>Bệnh viện 1A - lý thường kiệt</t>
+  </si>
+  <si>
+    <t>Ngọc Ngân</t>
+  </si>
+  <si>
+    <t>HD064793</t>
+  </si>
+  <si>
+    <t>87 duong so 79, tan quy</t>
+  </si>
+  <si>
+    <t>Kim Chúc</t>
+  </si>
+  <si>
+    <t>HD064725</t>
+  </si>
+  <si>
+    <t>Hẻm 18B/73 Nguyễn thị minh khai đakao</t>
+  </si>
+  <si>
+    <t>Chi Linh</t>
+  </si>
+  <si>
+    <t>HD064709</t>
+  </si>
+  <si>
+    <t>813 Trần Xuân Soạn</t>
+  </si>
+  <si>
+    <t>Nghi</t>
+  </si>
+  <si>
+    <t>HD064749</t>
+  </si>
+  <si>
+    <t>62 Nguyễn Văn Yến, p Tân Thới Hoà</t>
+  </si>
+  <si>
+    <t>Tranie Phan</t>
+  </si>
+  <si>
+    <t>HD064600</t>
+  </si>
+  <si>
+    <t>1041/19/7 Trần Xuân Soạn</t>
+  </si>
+  <si>
+    <t>Lê Thị Minh Phượng</t>
+  </si>
+  <si>
+    <t>HD064664</t>
+  </si>
+  <si>
+    <t>101/20 đường số 9 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Chau Nguyen</t>
+  </si>
+  <si>
+    <t>HD064811</t>
+  </si>
+  <si>
+    <t>2555 QL1A Phường Tân Hưng Thuận</t>
+  </si>
+  <si>
+    <t>MINZZY</t>
+  </si>
+  <si>
+    <t>XE TOÀN THẮNG VỀ CÀ PHÊ PHONG LONG THÀNH ĐỒNG NAI</t>
+  </si>
+  <si>
+    <t>HOANG ANH</t>
+  </si>
+  <si>
+    <t>385/4 quang trung p go vap</t>
+  </si>
+  <si>
+    <t>vi hồ</t>
+  </si>
+  <si>
+    <t>Nhà xe Minh Quốc</t>
+  </si>
+  <si>
+    <t>at 07-10</t>
+  </si>
+  <si>
+    <t>THU 4</t>
+  </si>
+  <si>
+    <t>NGAY 7-10</t>
   </si>
 </sst>
 </file>
@@ -3039,7 +3365,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="str" cm="1">
-        <f t="array" aca="1" ref="A3:A7" ca="1">_xlfn.LET(
+        <f t="array" aca="1" ref="A3:A8" ca="1">_xlfn.LET(
     _xlpm.start,DATE(B1,--_xlfn.TEXTAFTER(A1," "),1),
     _xlpm.d,_xlfn._xlws.FILTER(
         _xlfn.SEQUENCE(DAY(EOMONTH(_xlpm.start,0)),,_xlpm.start),
@@ -3167,14 +3493,17 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="3" t="str">
+        <f ca="1"/>
+        <v>07-10</v>
+      </c>
       <c r="B8" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;A8&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
@@ -3182,7 +3511,7 @@
       </c>
       <c r="E8" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3571,7 +3900,7 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">SUBTOTAL(9,E3:E28)</f>
-        <v>244</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3588,7 +3917,7 @@
         ),
     0)
 )</f>
-        <v>1083</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3597,7 +3926,7 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">-E29*2</f>
-        <v>-488</v>
+        <v>-560</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3606,7 +3935,7 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>595</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -17905,4 +18234,2191 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1489BF44-8EF7-4971-A5A2-1BCEF6DB9F6C}">
+  <dimension ref="A1:R65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="17" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>902</v>
+      </c>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>807</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>808</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>809</v>
+      </c>
+      <c r="F3" s="21">
+        <v>11</v>
+      </c>
+      <c r="G3" s="21">
+        <v>0</v>
+      </c>
+      <c r="H3" s="21">
+        <v>25</v>
+      </c>
+      <c r="I3" s="21">
+        <f t="shared" ref="I3:I39" si="0">G3-H3</f>
+        <v>-25</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8">
+        <f>H3</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>815</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>816</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>817</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="G4" s="21">
+        <v>825</v>
+      </c>
+      <c r="H4" s="21">
+        <v>35</v>
+      </c>
+      <c r="I4" s="21">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>818</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>819</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>820</v>
+      </c>
+      <c r="F5" s="21">
+        <v>11</v>
+      </c>
+      <c r="G5" s="21">
+        <v>3780</v>
+      </c>
+      <c r="H5" s="21">
+        <v>35</v>
+      </c>
+      <c r="I5" s="21">
+        <f t="shared" si="0"/>
+        <v>3745</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+      <c r="R5" s="8">
+        <f>H5</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>824</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>825</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>826</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="21">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>30</v>
+      </c>
+      <c r="I6" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+      <c r="R6" s="8">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>851</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>852</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>853</v>
+      </c>
+      <c r="F7" s="21">
+        <v>12</v>
+      </c>
+      <c r="G7" s="21">
+        <v>1380</v>
+      </c>
+      <c r="H7" s="21">
+        <v>30</v>
+      </c>
+      <c r="I7" s="21">
+        <f t="shared" si="0"/>
+        <v>1350</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>854</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>855</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>856</v>
+      </c>
+      <c r="F8" s="21">
+        <v>6</v>
+      </c>
+      <c r="G8" s="21">
+        <v>865</v>
+      </c>
+      <c r="H8" s="21">
+        <v>25</v>
+      </c>
+      <c r="I8" s="21">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>857</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>858</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>859</v>
+      </c>
+      <c r="F9" s="21">
+        <v>7</v>
+      </c>
+      <c r="G9" s="21">
+        <v>910</v>
+      </c>
+      <c r="H9" s="21">
+        <v>30</v>
+      </c>
+      <c r="I9" s="21">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>873</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>874</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>875</v>
+      </c>
+      <c r="F10" s="21">
+        <v>7</v>
+      </c>
+      <c r="G10" s="21">
+        <v>850</v>
+      </c>
+      <c r="H10" s="21">
+        <v>30</v>
+      </c>
+      <c r="I10" s="21">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>882</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>883</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>884</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="21">
+        <v>915</v>
+      </c>
+      <c r="H11" s="21">
+        <v>25</v>
+      </c>
+      <c r="I11" s="21">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>888</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>889</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>890</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="21">
+        <v>1410</v>
+      </c>
+      <c r="H12" s="21">
+        <v>30</v>
+      </c>
+      <c r="I12" s="21">
+        <f t="shared" si="0"/>
+        <v>1380</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>891</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>892</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>893</v>
+      </c>
+      <c r="F13" s="21">
+        <v>12</v>
+      </c>
+      <c r="G13" s="21">
+        <v>490</v>
+      </c>
+      <c r="H13" s="21">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>810</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>799</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>800</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>801</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="21">
+        <v>1340</v>
+      </c>
+      <c r="H14" s="21">
+        <v>20</v>
+      </c>
+      <c r="I14" s="21">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>805</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>806</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="21">
+        <v>12</v>
+      </c>
+      <c r="G15" s="21">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21">
+        <v>30</v>
+      </c>
+      <c r="I15" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+      <c r="R15" s="8">
+        <f>H15</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>811</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>812</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>813</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="21">
+        <v>1010</v>
+      </c>
+      <c r="H16" s="21">
+        <v>20</v>
+      </c>
+      <c r="I16" s="21">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>821</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>822</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>823</v>
+      </c>
+      <c r="F17" s="21">
+        <v>2</v>
+      </c>
+      <c r="G17" s="21">
+        <v>820</v>
+      </c>
+      <c r="H17" s="21">
+        <v>30</v>
+      </c>
+      <c r="I17" s="21">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>827</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>828</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>829</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="21">
+        <v>0</v>
+      </c>
+      <c r="H18" s="21">
+        <v>20</v>
+      </c>
+      <c r="I18" s="21">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+      <c r="R18" s="8">
+        <f>H18</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>836</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>837</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>838</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="21">
+        <v>1485</v>
+      </c>
+      <c r="H19" s="21">
+        <v>25</v>
+      </c>
+      <c r="I19" s="21">
+        <f t="shared" si="0"/>
+        <v>1460</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>842</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>843</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>844</v>
+      </c>
+      <c r="F20" s="21">
+        <v>9</v>
+      </c>
+      <c r="G20" s="21">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21">
+        <v>30</v>
+      </c>
+      <c r="I20" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+      <c r="R20" s="8">
+        <f>H20</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>845</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>846</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>847</v>
+      </c>
+      <c r="F21" s="21">
+        <v>12</v>
+      </c>
+      <c r="G21" s="21">
+        <v>1710</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f t="shared" si="0"/>
+        <v>1680</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>864</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>865</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>866</v>
+      </c>
+      <c r="F22" s="21">
+        <v>2</v>
+      </c>
+      <c r="G22" s="21">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21">
+        <v>30</v>
+      </c>
+      <c r="I22" s="21">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+      <c r="R22" s="8">
+        <f t="shared" ref="R22:R23" si="1">H22</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>894</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20" t="s">
+        <v>895</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="21">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>25</v>
+      </c>
+      <c r="I23" s="21">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+      <c r="R23" s="8">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>896</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>897</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="21">
+        <v>30</v>
+      </c>
+      <c r="H24" s="21">
+        <v>30</v>
+      </c>
+      <c r="I24" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>898</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20" t="s">
+        <v>899</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>40</v>
+      </c>
+      <c r="I25" s="21">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+      <c r="R25" s="8">
+        <f>H25</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>795</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>796</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>797</v>
+      </c>
+      <c r="F26" s="21">
+        <v>3</v>
+      </c>
+      <c r="G26" s="21">
+        <v>1765</v>
+      </c>
+      <c r="H26" s="21">
+        <v>25</v>
+      </c>
+      <c r="I26" s="21">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>803</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>804</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="21">
+        <v>365</v>
+      </c>
+      <c r="H27" s="21">
+        <v>25</v>
+      </c>
+      <c r="I27" s="21">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>814</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>804</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G28" s="21">
+        <v>0</v>
+      </c>
+      <c r="H28" s="21">
+        <v>0</v>
+      </c>
+      <c r="I28" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+      <c r="R28" s="8">
+        <f>H28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>830</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>831</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>832</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="21">
+        <v>480</v>
+      </c>
+      <c r="H29" s="21">
+        <v>20</v>
+      </c>
+      <c r="I29" s="21">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>833</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>834</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>835</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30" s="21">
+        <v>4520</v>
+      </c>
+      <c r="H30" s="21">
+        <v>35</v>
+      </c>
+      <c r="I30" s="21">
+        <f t="shared" si="0"/>
+        <v>4485</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M30" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20">
+        <v>1</v>
+      </c>
+      <c r="R30" s="8">
+        <f>H30</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>839</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>840</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>841</v>
+      </c>
+      <c r="F31" s="21">
+        <v>1</v>
+      </c>
+      <c r="G31" s="21">
+        <v>0</v>
+      </c>
+      <c r="H31" s="21">
+        <v>25</v>
+      </c>
+      <c r="I31" s="21">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20">
+        <v>1</v>
+      </c>
+      <c r="R31" s="8">
+        <f>H31</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>848</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>849</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>850</v>
+      </c>
+      <c r="F32" s="21">
+        <v>1</v>
+      </c>
+      <c r="G32" s="21">
+        <v>1015</v>
+      </c>
+      <c r="H32" s="21">
+        <v>25</v>
+      </c>
+      <c r="I32" s="21">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>860</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>861</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>862</v>
+      </c>
+      <c r="F33" s="21">
+        <v>3</v>
+      </c>
+      <c r="G33" s="21">
+        <v>1315</v>
+      </c>
+      <c r="H33" s="21">
+        <v>25</v>
+      </c>
+      <c r="I33" s="21">
+        <f t="shared" si="0"/>
+        <v>1290</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>710</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>863</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>712</v>
+      </c>
+      <c r="F34" s="25">
+        <v>3</v>
+      </c>
+      <c r="G34" s="25">
+        <v>0</v>
+      </c>
+      <c r="H34" s="25">
+        <v>25</v>
+      </c>
+      <c r="I34" s="25">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J34" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" s="24" t="s">
+        <v>798</v>
+      </c>
+      <c r="M34" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="24">
+        <v>1</v>
+      </c>
+      <c r="R34" s="34">
+        <f>H34</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>867</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>868</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>869</v>
+      </c>
+      <c r="F35" s="21">
+        <v>7</v>
+      </c>
+      <c r="G35" s="21">
+        <v>890</v>
+      </c>
+      <c r="H35" s="21">
+        <v>30</v>
+      </c>
+      <c r="I35" s="21">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>870</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>871</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>872</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" s="21">
+        <v>515</v>
+      </c>
+      <c r="H36" s="21">
+        <v>25</v>
+      </c>
+      <c r="I36" s="21">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>876</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>877</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>878</v>
+      </c>
+      <c r="F37" s="21">
+        <v>1</v>
+      </c>
+      <c r="G37" s="21">
+        <v>905</v>
+      </c>
+      <c r="H37" s="21">
+        <v>25</v>
+      </c>
+      <c r="I37" s="21">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>879</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>880</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>881</v>
+      </c>
+      <c r="F38" s="25">
+        <v>7</v>
+      </c>
+      <c r="G38" s="25">
+        <v>30</v>
+      </c>
+      <c r="H38" s="25">
+        <v>30</v>
+      </c>
+      <c r="I38" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L38" s="24" t="s">
+        <v>798</v>
+      </c>
+      <c r="M38" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="20"/>
+      <c r="B39" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>885</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>886</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>887</v>
+      </c>
+      <c r="F39" s="21">
+        <v>7</v>
+      </c>
+      <c r="G39" s="21">
+        <v>760</v>
+      </c>
+      <c r="H39" s="21">
+        <v>30</v>
+      </c>
+      <c r="I39" s="21">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>798</v>
+      </c>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D41" s="9">
+        <f>COUNTA(D3:D39)</f>
+        <v>34</v>
+      </c>
+      <c r="G41" s="9">
+        <f t="shared" ref="G41:Q41" si="2">SUBTOTAL(9,G3:G39)</f>
+        <v>30380</v>
+      </c>
+      <c r="H41" s="9">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="I41" s="9">
+        <f t="shared" si="2"/>
+        <v>29380</v>
+      </c>
+      <c r="J41" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O41" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="9">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H42">
+        <f>-6*17</f>
+        <v>-102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="45"/>
+      <c r="E43" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="H43">
+        <f>-4*25</f>
+        <v>-100</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="O43" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>798</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="46">
+        <f>SUMIFS(I$3:I$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
+        <v>29380</v>
+      </c>
+      <c r="D44" s="46"/>
+      <c r="E44" s="12">
+        <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
+        <v>37</v>
+      </c>
+      <c r="F44" t="s">
+        <v>194</v>
+      </c>
+      <c r="H44">
+        <f>-1*30</f>
+        <v>-30</v>
+      </c>
+      <c r="K44" t="s">
+        <v>195</v>
+      </c>
+      <c r="L44">
+        <f>SUMIFS(G$3:G$39,J$3:J$39,K$43)</f>
+        <v>12560</v>
+      </c>
+      <c r="M44">
+        <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$43)-INT(COUNTIFS(J$3:J$39,K$43,M$3:M$39,"*gộp*")/2)</f>
+        <v>13</v>
+      </c>
+      <c r="O44" t="s">
+        <v>30</v>
+      </c>
+      <c r="P44">
+        <f>L49</f>
+        <v>12280</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B45" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" s="47">
+        <v>0</v>
+      </c>
+      <c r="D45" s="47"/>
+      <c r="K45" t="s">
+        <v>197</v>
+      </c>
+      <c r="L45">
+        <f>-SUMIFS(H$3:H$39,J$3:J$39,K$43)+M45*5</f>
+        <v>-280</v>
+      </c>
+      <c r="M45">
+        <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$43)-INT(COUNTIFS(J$3:J$39,K$43,M$3:M$39,"*gộp*")/2)</f>
+        <v>13</v>
+      </c>
+      <c r="O45" t="s">
+        <v>31</v>
+      </c>
+      <c r="P45">
+        <f>L57</f>
+        <v>6053</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B46" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C46" s="47">
+        <f>-SUMIFS(I$3:I$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="47"/>
+      <c r="E46" s="13">
+        <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>200</v>
+      </c>
+      <c r="L46">
+        <f>-M46*2</f>
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <f>COUNTIFS(K$3:K$39,K$43,L$3:L$39,A$44)-(COUNTIFS(K$3:K$39,K$43,M$3:M$39,"*gộp*")/2)-COUNTIFS(K$3:K$39,K$43,M$3:M$39,"*đơn trả*")-COUNTIFS(K$3:K$39,K$43,M$3:M$39,"*hàng tỉnh*")</f>
+        <v>0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>900</v>
+      </c>
+      <c r="P46">
+        <f>L65</f>
+        <v>11193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B47" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C47" s="45">
+        <f>SUBTOTAL(9,C44:C46)</f>
+        <v>29380</v>
+      </c>
+      <c r="D47" s="45"/>
+      <c r="E47">
+        <f>E44</f>
+        <v>37</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="O47" t="s">
+        <v>203</v>
+      </c>
+      <c r="P47">
+        <f>-C51</f>
+        <v>-29380</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B48" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="K48" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="O48" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P48" s="10">
+        <f>SUBTOTAL(9,P44:P47)</f>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B49" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="L49" s="16">
+        <f>SUBTOTAL(9,L44:L48)</f>
+        <v>12280</v>
+      </c>
+      <c r="M49" s="16">
+        <f>M44</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C51" s="44">
+        <f>C47+C48+C49</f>
+        <v>29380</v>
+      </c>
+      <c r="D51" s="44"/>
+      <c r="E51" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>195</v>
+      </c>
+      <c r="L52">
+        <f>SUMIFS(G$3:G$39,J$3:J$39,K$51)</f>
+        <v>6395</v>
+      </c>
+      <c r="M52">
+        <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$51)-INT(COUNTIFS(J$3:J$39,K$51,M$3:M$39,"*gộp*")/2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
+        <v>197</v>
+      </c>
+      <c r="L53">
+        <f>-SUMIFS(H$3:H$39,J$3:J$39,K$51)+M53*5</f>
+        <v>-270</v>
+      </c>
+      <c r="M53">
+        <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$51)-INT(COUNTIFS(J$3:J$39,K$51,M$3:M$39,"*gộp*")/2)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K54" t="s">
+        <v>200</v>
+      </c>
+      <c r="L54">
+        <f>-M54*2</f>
+        <v>-72</v>
+      </c>
+      <c r="M54">
+        <f>COUNTIFS(K$3:K$39,K$51,L$3:L$39,A$44)-(COUNTIFS(K$3:K$39,K$51,M$3:M$39,"*gộp*")/2)-COUNTIFS(K$3:K$39,K$51,M$3:M$39,"*đơn trả*")-COUNTIFS(K$3:K$39,K$51,M$3:M$39,"*hàng tỉnh*")</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K55" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K56" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L57" s="16">
+        <f>SUBTOTAL(9,L52:L56)</f>
+        <v>6053</v>
+      </c>
+      <c r="M57" s="16">
+        <f>M52</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K59" s="11" t="s">
+        <v>810</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K60" t="s">
+        <v>195</v>
+      </c>
+      <c r="L60">
+        <f>SUMIFS(G$3:G$39,J$3:J$39,K$59)</f>
+        <v>11425</v>
+      </c>
+      <c r="M60">
+        <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$59)-INT(COUNTIFS(J$3:J$39,K$59,M$3:M$39,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K61" t="s">
+        <v>197</v>
+      </c>
+      <c r="L61">
+        <f>SUM(H42:H44)</f>
+        <v>-232</v>
+      </c>
+      <c r="M61">
+        <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$59)-INT(COUNTIFS(J$3:J$39,K$59,M$3:M$39,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K62" t="s">
+        <v>200</v>
+      </c>
+      <c r="L62">
+        <f>-M62*2</f>
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <f>COUNTIFS(K$3:K$39,K$59,L$3:L$39,A$44)-(COUNTIFS(K$3:K$39,K$59,M$3:M$39,"*gộp*")/2)-COUNTIFS(K$3:K$39,K$59,M$3:M$39,"*đơn trả*")-COUNTIFS(K$3:K$39,K$59,M$3:M$39,"*hàng tỉnh*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K63" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K64" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L65" s="16">
+        <f>SUBTOTAL(9,L60:L64)</f>
+        <v>11193</v>
+      </c>
+      <c r="M65" s="16">
+        <f>M60</f>
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P39" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P39">
+      <sortCondition ref="J2:J39"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
 </file>
--- a/data/Oct/InternalDailyReport_Oct.xlsx
+++ b/data/Oct/InternalDailyReport_Oct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C046F6-7BC3-4544-A595-BD982D1D058E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F73A3AB-A632-4ED7-8414-44F94574C42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="23" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="05-10" sheetId="27" r:id="rId5"/>
     <sheet name="06-10" sheetId="28" r:id="rId6"/>
     <sheet name="07-10" sheetId="29" r:id="rId7"/>
+    <sheet name="08-10" sheetId="30" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01-10'!$A$2:$P$53</definedName>
@@ -28,6 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05-10'!$A$2:$P$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06-10'!$A$2:$P$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'07-10'!$A$2:$P$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'08-10'!$A$2:$P$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2896" uniqueCount="965">
   <si>
     <t>NGÀY</t>
   </si>
@@ -2779,6 +2781,192 @@
   </si>
   <si>
     <t>NGAY 7-10</t>
+  </si>
+  <si>
+    <t>kh ck shop 825k</t>
+  </si>
+  <si>
+    <t>kh ck shop 730k</t>
+  </si>
+  <si>
+    <t>kh ck shop 1340k</t>
+  </si>
+  <si>
+    <t>Lữ Hạnh Hoàng Châu</t>
+  </si>
+  <si>
+    <t>HD064950</t>
+  </si>
+  <si>
+    <t>17 mai chí thọ phường an khánh New city - toa hawai 1</t>
+  </si>
+  <si>
+    <t>08-10-2026</t>
+  </si>
+  <si>
+    <t>HD065026</t>
+  </si>
+  <si>
+    <t>208 nguyễn hữu cảnh phường 22 chung cư vinhome tòa lanmark 5</t>
+  </si>
+  <si>
+    <t>Bonnie Ya</t>
+  </si>
+  <si>
+    <t>HD065049</t>
+  </si>
+  <si>
+    <t>932A1 Trường Sa, P. Nhiêu Lộc (ngay tiệm cafe giặt sấy Mộc - lên lầu 1 là tới studio)</t>
+  </si>
+  <si>
+    <t>Lin (Zalo)</t>
+  </si>
+  <si>
+    <t>HD064959</t>
+  </si>
+  <si>
+    <t>9 Đ. Nguyễn Trường Tộ, Xóm Chiếu</t>
+  </si>
+  <si>
+    <t>mimi (giao cho lễ tân báo hàng của Mimi)</t>
+  </si>
+  <si>
+    <t>HD065007</t>
+  </si>
+  <si>
+    <t>339/24B Đ. Lê Văn Sỹ, Phường 13</t>
+  </si>
+  <si>
+    <t>Phạm Huỳnh Duyên</t>
+  </si>
+  <si>
+    <t>HD065071</t>
+  </si>
+  <si>
+    <t>439/97/12 tân thới hiệp 21</t>
+  </si>
+  <si>
+    <t>Như Ý Nguyễn</t>
+  </si>
+  <si>
+    <t>4 Đào Trí, P. Phú Thuận</t>
+  </si>
+  <si>
+    <t>Khánh Hòa</t>
+  </si>
+  <si>
+    <t>HD064924</t>
+  </si>
+  <si>
+    <t>Ship đến saigon royal 9 Đ. Nguyễn Trường Tộ, Xóm Chiếu</t>
+  </si>
+  <si>
+    <t>Bảy nhận dùm My Trà</t>
+  </si>
+  <si>
+    <t>HD065006</t>
+  </si>
+  <si>
+    <t>32 đường 85 tân hưng</t>
+  </si>
+  <si>
+    <t>HD065035</t>
+  </si>
+  <si>
+    <t>SS3164-Mr.skill) SS Cargo Shipping (cờn dư 715k)</t>
+  </si>
+  <si>
+    <t>HD064963</t>
+  </si>
+  <si>
+    <t>674 đường số 2, Phường 13</t>
+  </si>
+  <si>
+    <t>AT 08-10</t>
+  </si>
+  <si>
+    <t>Trang Nguyễn</t>
+  </si>
+  <si>
+    <t>HD064863</t>
+  </si>
+  <si>
+    <t>76 Cù Lao</t>
+  </si>
+  <si>
+    <t>Linh Phùng</t>
+  </si>
+  <si>
+    <t>HD065046</t>
+  </si>
+  <si>
+    <t>491/24/22 nguyễn đình chiểu p2</t>
+  </si>
+  <si>
+    <t>Ngô thị Thu Thủy - fb Minh Minh Ng</t>
+  </si>
+  <si>
+    <t>HD064954</t>
+  </si>
+  <si>
+    <t>174/50 Lý chính Thắng.Phường Xuân Hòa</t>
+  </si>
+  <si>
+    <t>Trang Hồ Vĩnh Như</t>
+  </si>
+  <si>
+    <t>HD064899</t>
+  </si>
+  <si>
+    <t>35 đặng đức thuật, chung cư RIVERPARK PREMIER Block A, P. Tân Hưng</t>
+  </si>
+  <si>
+    <t>Khánh Vân</t>
+  </si>
+  <si>
+    <t>HD064868</t>
+  </si>
+  <si>
+    <t>77/39 Kinh Dương Vương F12</t>
+  </si>
+  <si>
+    <t>Trang Angels</t>
+  </si>
+  <si>
+    <t>HD064874</t>
+  </si>
+  <si>
+    <t>nhà 20 đường 2B phường Tân mỹ</t>
+  </si>
+  <si>
+    <t>Hanna Bui</t>
+  </si>
+  <si>
+    <t>HD064941</t>
+  </si>
+  <si>
+    <t>9B duong 16A Pbinh Hưng hòa A</t>
+  </si>
+  <si>
+    <t>số 42/43-45 Nguyễn Minh Hoàng, phường 12</t>
+  </si>
+  <si>
+    <t>TUYẾT NHI ZL2</t>
+  </si>
+  <si>
+    <t>170F Tân Hoà Đông f14</t>
+  </si>
+  <si>
+    <t>Em Na</t>
+  </si>
+  <si>
+    <t>16/2 THÁI THỊ NHẠN P10</t>
+  </si>
+  <si>
+    <t>at 08-10</t>
+  </si>
+  <si>
+    <t>NGAY 8-10</t>
   </si>
 </sst>
 </file>
@@ -2865,7 +3053,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2921,6 +3109,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2952,7 +3146,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3004,6 +3198,7 @@
     <xf numFmtId="3" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="10" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3365,7 +3560,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="str" cm="1">
-        <f t="array" aca="1" ref="A3:A8" ca="1">_xlfn.LET(
+        <f t="array" aca="1" ref="A3:A9" ca="1">_xlfn.LET(
     _xlpm.start,DATE(B1,--_xlfn.TEXTAFTER(A1," "),1),
     _xlpm.d,_xlfn._xlws.FILTER(
         _xlfn.SEQUENCE(DAY(EOMONTH(_xlpm.start,0)),,_xlpm.start),
@@ -3515,10 +3710,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
+      <c r="A9" s="3" t="str">
+        <f ca="1"/>
+        <v>08-10</v>
+      </c>
       <c r="B9" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4">
         <f t="shared" ca="1" si="2"/>
@@ -3530,7 +3728,7 @@
       </c>
       <c r="E9" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -3900,7 +4098,7 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">SUBTOTAL(9,E3:E28)</f>
-        <v>280</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3917,7 +4115,7 @@
         ),
     0)
 )</f>
-        <v>1229</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3926,7 +4124,7 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">-E29*2</f>
-        <v>-560</v>
+        <v>-608</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3935,7 +4133,7 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>669</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -6439,10 +6637,10 @@
       <c r="A57" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="D57" s="45"/>
+      <c r="D57" s="46"/>
       <c r="E57" s="10" t="s">
         <v>190</v>
       </c>
@@ -6470,11 +6668,11 @@
       <c r="B58" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C58" s="46">
+      <c r="C58" s="47">
         <f>SUMIFS(I$3:I$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>35480</v>
       </c>
-      <c r="D58" s="46"/>
+      <c r="D58" s="47"/>
       <c r="E58" s="12">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,L$3:L$53,A$58)</f>
         <v>49</v>
@@ -6509,10 +6707,10 @@
       <c r="B59" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C59" s="47">
-        <v>0</v>
-      </c>
-      <c r="D59" s="47"/>
+      <c r="C59" s="48">
+        <v>0</v>
+      </c>
+      <c r="D59" s="48"/>
       <c r="K59" t="s">
         <v>197</v>
       </c>
@@ -6536,11 +6734,11 @@
       <c r="B60" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="48">
         <f>-SUMIFS(I$3:I$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>-1485</v>
       </c>
-      <c r="D60" s="47"/>
+      <c r="D60" s="48"/>
       <c r="E60" s="13">
         <f>SUMIFS(Q$3:Q$53,B$3:B$53,A$57,P$3:P$53,"xx",N$3:N$53,"x")</f>
         <v>2</v>
@@ -6568,11 +6766,11 @@
       <c r="B61" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C61" s="45">
+      <c r="C61" s="46">
         <f>SUBTOTAL(9,C58:C60)</f>
         <v>33995</v>
       </c>
-      <c r="D61" s="45"/>
+      <c r="D61" s="46"/>
       <c r="E61">
         <f>E58</f>
         <v>49</v>
@@ -6598,8 +6796,8 @@
       <c r="B62" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C62" s="43"/>
-      <c r="D62" s="43"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
       <c r="K62" s="13" t="s">
         <v>205</v>
       </c>
@@ -6615,8 +6813,8 @@
       <c r="B63" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
       <c r="L63" s="16">
         <f>SUBTOTAL(9,L58:L62)</f>
         <v>10003</v>
@@ -6630,11 +6828,11 @@
       <c r="B65" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C65" s="44">
+      <c r="C65" s="45">
         <f>C61+C62+C63</f>
         <v>33995</v>
       </c>
-      <c r="D65" s="44"/>
+      <c r="D65" s="45"/>
       <c r="E65" s="9" t="s">
         <v>209</v>
       </c>
@@ -9128,10 +9326,10 @@
       <c r="A54" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="45" t="s">
+      <c r="C54" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="D54" s="45"/>
+      <c r="D54" s="46"/>
       <c r="E54" s="10" t="s">
         <v>190</v>
       </c>
@@ -9159,11 +9357,11 @@
       <c r="B55" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C55" s="46">
+      <c r="C55" s="47">
         <f>SUMIFS(I$3:I$50,B$3:B$50,A$54,L$3:L$50,A$55)</f>
         <v>33160</v>
       </c>
-      <c r="D55" s="46"/>
+      <c r="D55" s="47"/>
       <c r="E55" s="12">
         <f>SUMIFS(Q$3:Q$50,B$3:B$50,A$54,L$3:L$50,A$55)</f>
         <v>47</v>
@@ -9198,10 +9396,10 @@
       <c r="B56" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C56" s="47">
-        <v>0</v>
-      </c>
-      <c r="D56" s="47"/>
+      <c r="C56" s="48">
+        <v>0</v>
+      </c>
+      <c r="D56" s="48"/>
       <c r="K56" t="s">
         <v>197</v>
       </c>
@@ -9225,11 +9423,11 @@
       <c r="B57" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C57" s="47">
+      <c r="C57" s="48">
         <f>-SUMIFS(I$3:I$50,B$3:B$50,A$54,P$3:P$50,"xx",N$3:N$50,"x")</f>
         <v>-15</v>
       </c>
-      <c r="D57" s="47"/>
+      <c r="D57" s="48"/>
       <c r="E57" s="13">
         <f>SUMIFS(Q$3:Q$50,B$3:B$50,A$54,P$3:P$50,"xx",N$3:N$50,"x")</f>
         <v>1</v>
@@ -9257,11 +9455,11 @@
       <c r="B58" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C58" s="45">
+      <c r="C58" s="46">
         <f>SUBTOTAL(9,C55:C57)</f>
         <v>33145</v>
       </c>
-      <c r="D58" s="45"/>
+      <c r="D58" s="46"/>
       <c r="E58">
         <f>E55</f>
         <v>47</v>
@@ -9295,8 +9493,8 @@
       <c r="B60" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C60" s="43"/>
-      <c r="D60" s="43"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
       <c r="K60" s="13" t="s">
         <v>205</v>
       </c>
@@ -9312,8 +9510,8 @@
       <c r="B61" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C61" s="43"/>
-      <c r="D61" s="43"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="44"/>
       <c r="L61" s="16">
         <f>SUBTOTAL(9,L55:L60)</f>
         <v>7423</v>
@@ -9327,11 +9525,11 @@
       <c r="B63" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C63" s="44">
+      <c r="C63" s="45">
         <f>C58+C60+C61</f>
         <v>33145</v>
       </c>
-      <c r="D63" s="44"/>
+      <c r="D63" s="45"/>
       <c r="E63" s="9" t="s">
         <v>209</v>
       </c>
@@ -11081,10 +11279,10 @@
       <c r="A38" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="45" t="s">
+      <c r="C38" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="D38" s="45"/>
+      <c r="D38" s="46"/>
       <c r="E38" s="10" t="s">
         <v>190</v>
       </c>
@@ -11112,11 +11310,11 @@
       <c r="B39" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C39" s="46">
+      <c r="C39" s="47">
         <f>SUMIFS(I$3:I$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
         <v>20240</v>
       </c>
-      <c r="D39" s="46"/>
+      <c r="D39" s="47"/>
       <c r="E39" s="12">
         <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
         <v>31</v>
@@ -11151,10 +11349,10 @@
       <c r="B40" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C40" s="47">
-        <v>0</v>
-      </c>
-      <c r="D40" s="47"/>
+      <c r="C40" s="48">
+        <v>0</v>
+      </c>
+      <c r="D40" s="48"/>
       <c r="K40" t="s">
         <v>197</v>
       </c>
@@ -11178,11 +11376,11 @@
       <c r="B41" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="48">
         <f>-SUMIFS(I$3:I$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
         <v>-730</v>
       </c>
-      <c r="D41" s="47"/>
+      <c r="D41" s="48"/>
       <c r="E41" s="13">
         <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
         <v>1</v>
@@ -11210,11 +11408,11 @@
       <c r="B42" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C42" s="45">
+      <c r="C42" s="46">
         <f>SUBTOTAL(9,C39:C41)</f>
         <v>19510</v>
       </c>
-      <c r="D42" s="45"/>
+      <c r="D42" s="46"/>
       <c r="E42">
         <f>E39</f>
         <v>31</v>
@@ -11234,8 +11432,8 @@
       <c r="B43" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
       <c r="K43" s="13" t="s">
         <v>205</v>
       </c>
@@ -11251,8 +11449,8 @@
       <c r="B44" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
       <c r="L44" s="16">
         <f>SUBTOTAL(9,L39:L43)</f>
         <v>4190</v>
@@ -11266,11 +11464,11 @@
       <c r="B46" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C46" s="44">
+      <c r="C46" s="45">
         <f>C42+C43+C44</f>
         <v>19510</v>
       </c>
-      <c r="D46" s="44"/>
+      <c r="D46" s="45"/>
       <c r="E46" s="9" t="s">
         <v>209</v>
       </c>
@@ -15302,10 +15500,10 @@
       <c r="A88" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C88" s="45" t="s">
+      <c r="C88" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="D88" s="45"/>
+      <c r="D88" s="46"/>
       <c r="E88" s="10" t="s">
         <v>190</v>
       </c>
@@ -15333,11 +15531,11 @@
       <c r="B89" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C89" s="46">
+      <c r="C89" s="47">
         <f>SUMIFS(I$3:I$84,B$3:B$84,A$88,L$3:L$84,A$89)</f>
         <v>59285</v>
       </c>
-      <c r="D89" s="46"/>
+      <c r="D89" s="47"/>
       <c r="E89" s="12">
         <f>SUMIFS(Q$3:Q$84,B$3:B$84,A$88,L$3:L$84,A$89)</f>
         <v>82</v>
@@ -15372,10 +15570,10 @@
       <c r="B90" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C90" s="47">
-        <v>0</v>
-      </c>
-      <c r="D90" s="47"/>
+      <c r="C90" s="48">
+        <v>0</v>
+      </c>
+      <c r="D90" s="48"/>
       <c r="K90" t="s">
         <v>197</v>
       </c>
@@ -15399,11 +15597,11 @@
       <c r="B91" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C91" s="47">
+      <c r="C91" s="48">
         <f>-SUMIFS(I$3:I$84,B$3:B$84,A$88,P$3:P$84,"xx",N$3:N$84,"x")</f>
         <v>-3490</v>
       </c>
-      <c r="D91" s="47"/>
+      <c r="D91" s="48"/>
       <c r="E91" s="13">
         <f>SUMIFS(Q$3:Q$84,B$3:B$84,A$88,P$3:P$84,"xx",N$3:N$84,"x")</f>
         <v>2</v>
@@ -15431,11 +15629,11 @@
       <c r="B92" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C92" s="45">
+      <c r="C92" s="46">
         <f>SUBTOTAL(9,C89:C91)</f>
         <v>55795</v>
       </c>
-      <c r="D92" s="45"/>
+      <c r="D92" s="46"/>
       <c r="E92">
         <f>E89</f>
         <v>82</v>
@@ -15455,8 +15653,8 @@
       <c r="B93" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C93" s="43"/>
-      <c r="D93" s="43"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="44"/>
       <c r="K93" s="13" t="s">
         <v>205</v>
       </c>
@@ -15472,8 +15670,8 @@
       <c r="B94" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C94" s="43"/>
-      <c r="D94" s="43"/>
+      <c r="C94" s="44"/>
+      <c r="D94" s="44"/>
       <c r="L94" s="16">
         <f>SUBTOTAL(9,L89:L93)</f>
         <v>16778</v>
@@ -15487,11 +15685,11 @@
       <c r="B96" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C96" s="44">
+      <c r="C96" s="45">
         <f>C92+C93+C94</f>
         <v>55795</v>
       </c>
-      <c r="D96" s="44"/>
+      <c r="D96" s="45"/>
       <c r="E96" s="9" t="s">
         <v>209</v>
       </c>
@@ -17861,10 +18059,10 @@
       <c r="A51" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="45" t="s">
+      <c r="C51" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="D51" s="45"/>
+      <c r="D51" s="46"/>
       <c r="E51" s="10" t="s">
         <v>190</v>
       </c>
@@ -17892,11 +18090,11 @@
       <c r="B52" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C52" s="46">
+      <c r="C52" s="47">
         <f>SUMIFS(I$3:I$47,B$3:B$47,A$51,L$3:L$47,A$52)</f>
         <v>26130</v>
       </c>
-      <c r="D52" s="46"/>
+      <c r="D52" s="47"/>
       <c r="E52" s="12">
         <f>SUMIFS(Q$3:Q$47,B$3:B$47,A$51,L$3:L$47,A$52)</f>
         <v>43</v>
@@ -17931,10 +18129,10 @@
       <c r="B53" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C53" s="47">
-        <v>0</v>
-      </c>
-      <c r="D53" s="47"/>
+      <c r="C53" s="48">
+        <v>0</v>
+      </c>
+      <c r="D53" s="48"/>
       <c r="K53" t="s">
         <v>197</v>
       </c>
@@ -17958,11 +18156,11 @@
       <c r="B54" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C54" s="47">
+      <c r="C54" s="48">
         <f>-SUMIFS(I$3:I$47,B$3:B$47,A$51,P$3:P$47,"xx",N$3:N$47,"x")</f>
         <v>-2495</v>
       </c>
-      <c r="D54" s="47"/>
+      <c r="D54" s="48"/>
       <c r="E54" s="13">
         <f>SUMIFS(Q$3:Q$47,B$3:B$47,A$51,P$3:P$47,"xx",N$3:N$47,"x")</f>
         <v>2</v>
@@ -17990,11 +18188,11 @@
       <c r="B55" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C55" s="45">
+      <c r="C55" s="46">
         <f>SUBTOTAL(9,C52:C54)</f>
         <v>23635</v>
       </c>
-      <c r="D55" s="45"/>
+      <c r="D55" s="46"/>
       <c r="E55">
         <f>E52</f>
         <v>43</v>
@@ -18014,8 +18212,8 @@
       <c r="B56" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C56" s="43"/>
-      <c r="D56" s="43"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
       <c r="K56" s="13" t="s">
         <v>205</v>
       </c>
@@ -18031,8 +18229,8 @@
       <c r="B57" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C57" s="43"/>
-      <c r="D57" s="43"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
       <c r="L57" s="16">
         <f>SUBTOTAL(9,L52:L56)</f>
         <v>12431</v>
@@ -18046,11 +18244,11 @@
       <c r="B59" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C59" s="44">
+      <c r="C59" s="45">
         <f>C55+C56+C57</f>
         <v>23635</v>
       </c>
-      <c r="D59" s="44"/>
+      <c r="D59" s="45"/>
       <c r="E59" s="9" t="s">
         <v>209</v>
       </c>
@@ -18253,7 +18451,7 @@
     <col min="10" max="10" width="9.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" customWidth="1"/>
     <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
@@ -18385,14 +18583,14 @@
         <v>218</v>
       </c>
       <c r="G4" s="21">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="H4" s="21">
         <v>35</v>
       </c>
       <c r="I4" s="21">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>-35</v>
       </c>
       <c r="J4" s="20" t="s">
         <v>810</v>
@@ -18403,12 +18601,18 @@
       <c r="L4" s="20" t="s">
         <v>798</v>
       </c>
-      <c r="M4" s="20"/>
+      <c r="M4" s="23" t="s">
+        <v>903</v>
+      </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
       <c r="Q4" s="20">
         <v>1</v>
+      </c>
+      <c r="R4" s="8">
+        <f>H4</f>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -18835,14 +19039,14 @@
         <v>77</v>
       </c>
       <c r="G14" s="21">
-        <v>1340</v>
+        <v>0</v>
       </c>
       <c r="H14" s="21">
         <v>20</v>
       </c>
       <c r="I14" s="21">
         <f t="shared" si="0"/>
-        <v>1320</v>
+        <v>-20</v>
       </c>
       <c r="J14" s="20" t="s">
         <v>31</v>
@@ -18853,12 +19057,18 @@
       <c r="L14" s="20" t="s">
         <v>798</v>
       </c>
-      <c r="M14" s="20"/>
+      <c r="M14" s="23" t="s">
+        <v>905</v>
+      </c>
       <c r="N14" s="20"/>
       <c r="O14" s="20"/>
       <c r="P14" s="20"/>
       <c r="Q14" s="20">
         <v>1</v>
+      </c>
+      <c r="R14" s="8">
+        <f>H14</f>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -19985,14 +20195,14 @@
         <v>7</v>
       </c>
       <c r="G39" s="21">
-        <v>760</v>
+        <v>30</v>
       </c>
       <c r="H39" s="21">
         <v>30</v>
       </c>
       <c r="I39" s="21">
         <f t="shared" si="0"/>
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>30</v>
@@ -20003,7 +20213,9 @@
       <c r="L39" s="20" t="s">
         <v>798</v>
       </c>
-      <c r="M39" s="20"/>
+      <c r="M39" s="43" t="s">
+        <v>904</v>
+      </c>
       <c r="N39" s="20"/>
       <c r="O39" s="20"/>
       <c r="P39" s="20"/>
@@ -20018,7 +20230,7 @@
       </c>
       <c r="G41" s="9">
         <f t="shared" ref="G41:Q41" si="2">SUBTOTAL(9,G3:G39)</f>
-        <v>30380</v>
+        <v>27485</v>
       </c>
       <c r="H41" s="9">
         <f t="shared" si="2"/>
@@ -20026,7 +20238,7 @@
       </c>
       <c r="I41" s="9">
         <f t="shared" si="2"/>
-        <v>29380</v>
+        <v>26485</v>
       </c>
       <c r="J41" s="9">
         <f t="shared" si="2"/>
@@ -20071,10 +20283,10 @@
       <c r="A43" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C43" s="45" t="s">
+      <c r="C43" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="D43" s="45"/>
+      <c r="D43" s="46"/>
       <c r="E43" s="10" t="s">
         <v>190</v>
       </c>
@@ -20102,11 +20314,11 @@
       <c r="B44" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C44" s="46">
+      <c r="C44" s="47">
         <f>SUMIFS(I$3:I$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
-        <v>29380</v>
-      </c>
-      <c r="D44" s="46"/>
+        <v>26485</v>
+      </c>
+      <c r="D44" s="47"/>
       <c r="E44" s="12">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,L$3:L$39,A$44)</f>
         <v>37</v>
@@ -20123,7 +20335,7 @@
       </c>
       <c r="L44">
         <f>SUMIFS(G$3:G$39,J$3:J$39,K$43)</f>
-        <v>12560</v>
+        <v>11830</v>
       </c>
       <c r="M44">
         <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$43)-INT(COUNTIFS(J$3:J$39,K$43,M$3:M$39,"*gộp*")/2)</f>
@@ -20134,17 +20346,17 @@
       </c>
       <c r="P44">
         <f>L49</f>
-        <v>12280</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B45" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C45" s="47">
-        <v>0</v>
-      </c>
-      <c r="D45" s="47"/>
+      <c r="C45" s="48">
+        <v>0</v>
+      </c>
+      <c r="D45" s="48"/>
       <c r="K45" t="s">
         <v>197</v>
       </c>
@@ -20161,18 +20373,18 @@
       </c>
       <c r="P45">
         <f>L57</f>
-        <v>6053</v>
+        <v>4713</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B46" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="48">
         <f>-SUMIFS(I$3:I$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>0</v>
       </c>
-      <c r="D46" s="47"/>
+      <c r="D46" s="48"/>
       <c r="E46" s="13">
         <f>SUMIFS(Q$3:Q$39,B$3:B$39,A$43,P$3:P$39,"xx",N$3:N$39,"x")</f>
         <v>0</v>
@@ -20193,18 +20405,18 @@
       </c>
       <c r="P46">
         <f>L65</f>
-        <v>11193</v>
+        <v>10368</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B47" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C47" s="45">
+      <c r="C47" s="46">
         <f>SUBTOTAL(9,C44:C46)</f>
-        <v>29380</v>
-      </c>
-      <c r="D47" s="45"/>
+        <v>26485</v>
+      </c>
+      <c r="D47" s="46"/>
       <c r="E47">
         <f>E44</f>
         <v>37</v>
@@ -20217,15 +20429,15 @@
       </c>
       <c r="P47">
         <f>-C51</f>
-        <v>-29380</v>
+        <v>-26485</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B48" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
       <c r="K48" s="13" t="s">
         <v>205</v>
       </c>
@@ -20241,11 +20453,11 @@
       <c r="B49" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
       <c r="L49" s="16">
         <f>SUBTOTAL(9,L44:L48)</f>
-        <v>12280</v>
+        <v>11550</v>
       </c>
       <c r="M49" s="16">
         <f>M44</f>
@@ -20256,11 +20468,11 @@
       <c r="B51" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C51" s="44">
+      <c r="C51" s="45">
         <f>C47+C48+C49</f>
-        <v>29380</v>
-      </c>
-      <c r="D51" s="44"/>
+        <v>26485</v>
+      </c>
+      <c r="D51" s="45"/>
       <c r="E51" s="9" t="s">
         <v>209</v>
       </c>
@@ -20280,7 +20492,7 @@
       </c>
       <c r="L52">
         <f>SUMIFS(G$3:G$39,J$3:J$39,K$51)</f>
-        <v>6395</v>
+        <v>5055</v>
       </c>
       <c r="M52">
         <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$51)-INT(COUNTIFS(J$3:J$39,K$51,M$3:M$39,"*gộp*")/2)</f>
@@ -20326,7 +20538,7 @@
     <row r="57" spans="2:13" x14ac:dyDescent="0.25">
       <c r="L57" s="16">
         <f>SUBTOTAL(9,L52:L56)</f>
-        <v>6053</v>
+        <v>4713</v>
       </c>
       <c r="M57" s="16">
         <f>M52</f>
@@ -20350,7 +20562,7 @@
       </c>
       <c r="L60">
         <f>SUMIFS(G$3:G$39,J$3:J$39,K$59)</f>
-        <v>11425</v>
+        <v>10600</v>
       </c>
       <c r="M60">
         <f>SUMIFS(Q$3:Q$39,J$3:J$39,K$59)-INT(COUNTIFS(J$3:J$39,K$59,M$3:M$39,"*gộp*")/2)</f>
@@ -20396,7 +20608,7 @@
     <row r="65" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L65" s="16">
         <f>SUBTOTAL(9,L60:L64)</f>
-        <v>11193</v>
+        <v>10368</v>
       </c>
       <c r="M65" s="16">
         <f>M60</f>
@@ -20421,4 +20633,1575 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D8FBE9-456A-42BA-958B-C36BDB39B97A}">
+  <dimension ref="A1:R52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="44.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="74.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>964</v>
+      </c>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>933</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>934</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>935</v>
+      </c>
+      <c r="F3" s="21">
+        <v>6</v>
+      </c>
+      <c r="G3" s="21">
+        <v>0</v>
+      </c>
+      <c r="H3" s="21">
+        <v>25</v>
+      </c>
+      <c r="I3" s="21">
+        <f>G3-H3</f>
+        <v>-25</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8">
+        <f>H3</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>949</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>950</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>951</v>
+      </c>
+      <c r="F4" s="21">
+        <v>6</v>
+      </c>
+      <c r="G4" s="21">
+        <v>1105</v>
+      </c>
+      <c r="H4" s="21">
+        <v>25</v>
+      </c>
+      <c r="I4" s="21">
+        <f>G4-H4</f>
+        <v>1080</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>957</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="21">
+        <v>1120</v>
+      </c>
+      <c r="H5" s="21">
+        <v>30</v>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v>1090</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="21">
+        <v>2355</v>
+      </c>
+      <c r="H6" s="21">
+        <v>35</v>
+      </c>
+      <c r="I6" s="21">
+        <f>G6-H6</f>
+        <v>2320</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>959</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20" t="s">
+        <v>960</v>
+      </c>
+      <c r="F7" s="21">
+        <v>6</v>
+      </c>
+      <c r="G7" s="21">
+        <v>7030</v>
+      </c>
+      <c r="H7" s="21">
+        <v>50</v>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v>6980</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="F8" s="21">
+        <v>6</v>
+      </c>
+      <c r="G8" s="21">
+        <v>30</v>
+      </c>
+      <c r="H8" s="21">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21">
+        <f>G8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>906</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>907</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>908</v>
+      </c>
+      <c r="F9" s="21">
+        <v>2</v>
+      </c>
+      <c r="G9" s="21">
+        <v>920</v>
+      </c>
+      <c r="H9" s="21">
+        <v>30</v>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v>890</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>911</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="21">
+        <v>940</v>
+      </c>
+      <c r="H10" s="21">
+        <v>20</v>
+      </c>
+      <c r="I10" s="21">
+        <f>G10-H10</f>
+        <v>920</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>921</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>922</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>923</v>
+      </c>
+      <c r="F11" s="21">
+        <v>12</v>
+      </c>
+      <c r="G11" s="21">
+        <v>790</v>
+      </c>
+      <c r="H11" s="21">
+        <v>30</v>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v>760</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>924</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="s">
+        <v>925</v>
+      </c>
+      <c r="F12" s="21">
+        <v>7</v>
+      </c>
+      <c r="G12" s="21">
+        <v>30</v>
+      </c>
+      <c r="H12" s="21">
+        <v>30</v>
+      </c>
+      <c r="I12" s="21">
+        <f>G12-H12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>784</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20" t="s">
+        <v>958</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" s="21">
+        <v>30</v>
+      </c>
+      <c r="H13" s="21">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21">
+        <f>G13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>961</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20" t="s">
+        <v>962</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" s="21">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>40</v>
+      </c>
+      <c r="I14" s="21">
+        <f>G14-H14</f>
+        <v>-40</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+      <c r="R14" s="8">
+        <f>H14</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="21">
+        <v>4710</v>
+      </c>
+      <c r="H15" s="21">
+        <v>50</v>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v>4660</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>912</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>914</v>
+      </c>
+      <c r="F16" s="21">
+        <v>3</v>
+      </c>
+      <c r="G16" s="21">
+        <v>945</v>
+      </c>
+      <c r="H16" s="21">
+        <v>25</v>
+      </c>
+      <c r="I16" s="21">
+        <f>G16-H16</f>
+        <v>920</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>916</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>917</v>
+      </c>
+      <c r="F17" s="21">
+        <v>4</v>
+      </c>
+      <c r="G17" s="21">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21">
+        <v>25</v>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v>-25</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+      <c r="R17" s="8">
+        <f t="shared" ref="R17:R18" si="0">H17</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>918</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>919</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>920</v>
+      </c>
+      <c r="F18" s="21">
+        <v>3</v>
+      </c>
+      <c r="G18" s="21">
+        <v>0</v>
+      </c>
+      <c r="H18" s="21">
+        <v>25</v>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v>-25</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>926</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>927</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>928</v>
+      </c>
+      <c r="F19" s="21">
+        <v>4</v>
+      </c>
+      <c r="G19" s="21">
+        <v>485</v>
+      </c>
+      <c r="H19" s="21">
+        <v>25</v>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v>460</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>929</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>930</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>931</v>
+      </c>
+      <c r="F20" s="21">
+        <v>7</v>
+      </c>
+      <c r="G20" s="21">
+        <v>800</v>
+      </c>
+      <c r="H20" s="21">
+        <v>30</v>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v>770</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>487</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>932</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>489</v>
+      </c>
+      <c r="F21" s="21">
+        <v>7</v>
+      </c>
+      <c r="G21" s="21">
+        <v>490</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v>460</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>938</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>939</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="21">
+        <v>810</v>
+      </c>
+      <c r="H22" s="21">
+        <v>20</v>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v>790</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>940</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>941</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>942</v>
+      </c>
+      <c r="F23" s="21">
+        <v>3</v>
+      </c>
+      <c r="G23" s="21">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>25</v>
+      </c>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+      <c r="R23" s="8">
+        <f>H23</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>943</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>944</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>945</v>
+      </c>
+      <c r="F24" s="21">
+        <v>3</v>
+      </c>
+      <c r="G24" s="21">
+        <v>815</v>
+      </c>
+      <c r="H24" s="21">
+        <v>25</v>
+      </c>
+      <c r="I24" s="21">
+        <f>G24-H24</f>
+        <v>790</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>946</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>947</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>948</v>
+      </c>
+      <c r="F25" s="21">
+        <v>7</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
+        <v>30</v>
+      </c>
+      <c r="I25" s="21">
+        <f>G25-H25</f>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+      <c r="R25" s="8">
+        <f>H25</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>952</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>953</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="F26" s="21">
+        <v>7</v>
+      </c>
+      <c r="G26" s="21">
+        <v>650</v>
+      </c>
+      <c r="H26" s="21">
+        <v>30</v>
+      </c>
+      <c r="I26" s="21">
+        <f>G26-H26</f>
+        <v>620</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>909</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D28" s="9">
+        <f>COUNTA(D3:D26)</f>
+        <v>17</v>
+      </c>
+      <c r="G28" s="9">
+        <f t="shared" ref="G28:Q28" si="1">SUBTOTAL(9,G3:G26)</f>
+        <v>24055</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" si="1"/>
+        <v>715</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="1"/>
+        <v>23340</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="9">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <f>-4*17</f>
+        <v>-68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="46"/>
+      <c r="E30" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="H30">
+        <f>-2*25</f>
+        <v>-50</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="O30" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>909</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="47">
+        <f>SUMIFS(I$3:I$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
+        <v>23340</v>
+      </c>
+      <c r="D31" s="47"/>
+      <c r="E31" s="12">
+        <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,L$3:L$26,A$31)</f>
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>194</v>
+      </c>
+      <c r="K31" t="s">
+        <v>195</v>
+      </c>
+      <c r="L31">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$30)</f>
+        <v>7420</v>
+      </c>
+      <c r="M31">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$30)-INT(COUNTIFS(J$3:J$26,K$30,M$3:M$26,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+      <c r="O31" t="s">
+        <v>31</v>
+      </c>
+      <c r="P31">
+        <f>L36</f>
+        <v>7177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B32" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" s="48">
+        <v>0</v>
+      </c>
+      <c r="D32" s="48"/>
+      <c r="K32" t="s">
+        <v>197</v>
+      </c>
+      <c r="L32">
+        <f>-SUMIFS(H$3:H$26,J$3:J$26,K$30)+M32*5</f>
+        <v>-195</v>
+      </c>
+      <c r="M32">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$30)-INT(COUNTIFS(J$3:J$26,K$30,M$3:M$26,"*gộp*")/2)</f>
+        <v>7</v>
+      </c>
+      <c r="O32" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32">
+        <f>L44</f>
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" s="48">
+        <f>-SUMIFS(I$3:I$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="48"/>
+      <c r="E33" s="13">
+        <f>SUMIFS(Q$3:Q$26,B$3:B$26,A$30,P$3:P$26,"xx",N$3:N$26,"x")</f>
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>200</v>
+      </c>
+      <c r="L33">
+        <f>-M33*2</f>
+        <v>-48</v>
+      </c>
+      <c r="M33">
+        <f>COUNTIFS(K$3:K$26,K$30,L$3:L$26,A$31)-(COUNTIFS(K$3:K$26,K$30,M$3:M$26,"*gộp*")/2)-COUNTIFS(K$3:K$26,K$30,M$3:M$26,"*đơn trả*")-COUNTIFS(K$3:K$26,K$30,M$3:M$26,"*hàng tỉnh*")</f>
+        <v>24</v>
+      </c>
+      <c r="O33" t="s">
+        <v>963</v>
+      </c>
+      <c r="P33">
+        <f>L52</f>
+        <v>11522</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="46">
+        <f>SUBTOTAL(9,C31:C33)</f>
+        <v>23340</v>
+      </c>
+      <c r="D34" s="46"/>
+      <c r="E34">
+        <f>E31</f>
+        <v>24</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="O34" t="s">
+        <v>203</v>
+      </c>
+      <c r="P34">
+        <f>-C38</f>
+        <v>-23340</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="K35" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P35" s="10">
+        <f>SUBTOTAL(9,P31:P34)</f>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="L36" s="16">
+        <f>SUBTOTAL(9,L31:L35)</f>
+        <v>7177</v>
+      </c>
+      <c r="M36" s="16">
+        <f>M31</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="45">
+        <f>C34+C35+C36</f>
+        <v>23340</v>
+      </c>
+      <c r="D38" s="45"/>
+      <c r="E38" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>195</v>
+      </c>
+      <c r="L39">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$38)</f>
+        <v>4995</v>
+      </c>
+      <c r="M39">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$38)-INT(COUNTIFS(J$3:J$26,K$38,M$3:M$26,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>197</v>
+      </c>
+      <c r="L40">
+        <f>-SUMIFS(H$3:H$26,J$3:J$26,K$38)+M40*5</f>
+        <v>-235</v>
+      </c>
+      <c r="M40">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$38)-INT(COUNTIFS(J$3:J$26,K$38,M$3:M$26,"*gộp*")/2)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>200</v>
+      </c>
+      <c r="L41">
+        <f>-M41*2</f>
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f>COUNTIFS(K$3:K$26,K$38,L$3:L$26,A$31)-(COUNTIFS(K$3:K$26,K$38,M$3:M$26,"*gộp*")/2)-COUNTIFS(K$3:K$26,K$38,M$3:M$26,"*đơn trả*")-COUNTIFS(K$3:K$26,K$38,M$3:M$26,"*hàng tỉnh*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K42" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K43" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L44" s="16">
+        <f>SUBTOTAL(9,L39:L43)</f>
+        <v>4760</v>
+      </c>
+      <c r="M44" s="16">
+        <f>M39</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K46" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>195</v>
+      </c>
+      <c r="L47">
+        <f>SUMIFS(G$3:G$26,J$3:J$26,K$46)</f>
+        <v>11640</v>
+      </c>
+      <c r="M47">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$46)-INT(COUNTIFS(J$3:J$26,K$46,M$3:M$26,"*gộp*")/2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>197</v>
+      </c>
+      <c r="L48">
+        <f>SUM(H29:H30)</f>
+        <v>-118</v>
+      </c>
+      <c r="M48">
+        <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$46)-INT(COUNTIFS(J$3:J$26,K$46,M$3:M$26,"*gộp*")/2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>200</v>
+      </c>
+      <c r="L49">
+        <f>-M49*2</f>
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <f>COUNTIFS(K$3:K$26,K$46,L$3:L$26,A$31)-(COUNTIFS(K$3:K$26,K$46,M$3:M$26,"*gộp*")/2)-COUNTIFS(K$3:K$26,K$46,M$3:M$26,"*đơn trả*")-COUNTIFS(K$3:K$26,K$46,M$3:M$26,"*hàng tỉnh*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L52" s="16">
+        <f>SUBTOTAL(9,L47:L51)</f>
+        <v>11522</v>
+      </c>
+      <c r="M52" s="16">
+        <f>M47</f>
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P26" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P26">
+      <sortCondition ref="J2:J26"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
 </file>
--- a/data/Oct/InternalDailyReport_Oct.xlsx
+++ b/data/Oct/InternalDailyReport_Oct.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F73A3AB-A632-4ED7-8414-44F94574C42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1C55AC-99E9-4F09-AABC-9EDD0DC59E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21119,19 +21119,21 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
+      <c r="A12" s="20" t="s">
+        <v>26</v>
+      </c>
       <c r="B12" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>924</v>
+        <v>784</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20" t="s">
-        <v>925</v>
-      </c>
-      <c r="F12" s="21">
-        <v>7</v>
+        <v>958</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>151</v>
       </c>
       <c r="G12" s="21">
         <v>30</v>
@@ -21152,9 +21154,7 @@
       <c r="L12" s="20" t="s">
         <v>909</v>
       </c>
-      <c r="M12" s="20" t="s">
-        <v>84</v>
-      </c>
+      <c r="M12" s="20"/>
       <c r="N12" s="20"/>
       <c r="O12" s="20"/>
       <c r="P12" s="20"/>
@@ -21170,24 +21170,24 @@
         <v>27</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>784</v>
+        <v>961</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="20" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>151</v>
       </c>
       <c r="G13" s="21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" s="21">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I13" s="21">
         <f>G13-H13</f>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>31</v>
@@ -21214,24 +21214,24 @@
         <v>27</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>961</v>
+        <v>40</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20" t="s">
-        <v>962</v>
+        <v>41</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="G14" s="21">
-        <v>0</v>
+        <v>4710</v>
       </c>
       <c r="H14" s="21">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I14" s="21">
         <f>G14-H14</f>
-        <v>-40</v>
+        <v>4660</v>
       </c>
       <c r="J14" s="20" t="s">
         <v>31</v>
@@ -21251,50 +21251,50 @@
       </c>
       <c r="R14" s="8">
         <f>H14</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="21">
-        <v>4710</v>
-      </c>
-      <c r="H15" s="21">
         <v>50</v>
       </c>
-      <c r="I15" s="21">
+    </row>
+    <row r="15" spans="1:18" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24"/>
+      <c r="B15" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>924</v>
+      </c>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24" t="s">
+        <v>925</v>
+      </c>
+      <c r="F15" s="25">
+        <v>7</v>
+      </c>
+      <c r="G15" s="25">
+        <v>30</v>
+      </c>
+      <c r="H15" s="25">
+        <v>30</v>
+      </c>
+      <c r="I15" s="25">
         <f>G15-H15</f>
-        <v>4660</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="L15" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="24" t="s">
         <v>909</v>
       </c>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20">
+      <c r="M15" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24">
         <v>1</v>
       </c>
     </row>
@@ -21906,18 +21906,18 @@
       </c>
       <c r="L31">
         <f>SUMIFS(G$3:G$26,J$3:J$26,K$30)</f>
-        <v>7420</v>
+        <v>7390</v>
       </c>
       <c r="M31">
         <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$30)-INT(COUNTIFS(J$3:J$26,K$30,M$3:M$26,"*gộp*")/2)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O31" t="s">
         <v>31</v>
       </c>
       <c r="P31">
         <f>L36</f>
-        <v>7177</v>
+        <v>7172</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -21933,18 +21933,18 @@
       </c>
       <c r="L32">
         <f>-SUMIFS(H$3:H$26,J$3:J$26,K$30)+M32*5</f>
-        <v>-195</v>
+        <v>-170</v>
       </c>
       <c r="M32">
         <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$30)-INT(COUNTIFS(J$3:J$26,K$30,M$3:M$26,"*gộp*")/2)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O32" t="s">
         <v>30</v>
       </c>
       <c r="P32">
         <f>L44</f>
-        <v>4760</v>
+        <v>4765</v>
       </c>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.25">
@@ -22028,11 +22028,11 @@
       <c r="D36" s="44"/>
       <c r="L36" s="16">
         <f>SUBTOTAL(9,L31:L35)</f>
-        <v>7177</v>
+        <v>7172</v>
       </c>
       <c r="M36" s="16">
         <f>M31</f>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
@@ -22063,11 +22063,11 @@
       </c>
       <c r="L39">
         <f>SUMIFS(G$3:G$26,J$3:J$26,K$38)</f>
-        <v>4995</v>
+        <v>5025</v>
       </c>
       <c r="M39">
         <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$38)-INT(COUNTIFS(J$3:J$26,K$38,M$3:M$26,"*gộp*")/2)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
@@ -22076,11 +22076,11 @@
       </c>
       <c r="L40">
         <f>-SUMIFS(H$3:H$26,J$3:J$26,K$38)+M40*5</f>
-        <v>-235</v>
+        <v>-260</v>
       </c>
       <c r="M40">
         <f>SUMIFS(Q$3:Q$26,J$3:J$26,K$38)-INT(COUNTIFS(J$3:J$26,K$38,M$3:M$26,"*gộp*")/2)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.25">
@@ -22109,11 +22109,11 @@
     <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="L44" s="16">
         <f>SUBTOTAL(9,L39:L43)</f>
-        <v>4760</v>
+        <v>4765</v>
       </c>
       <c r="M44" s="16">
         <f>M39</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.25">

--- a/data/Oct/InternalDailyReport_Oct.xlsx
+++ b/data/Oct/InternalDailyReport_Oct.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4F8127-132A-41D5-9146-2828FEA5E497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4963B5A-BBFE-4AFF-A16B-7E4ACB42C8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5811" uniqueCount="1750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5813" uniqueCount="1752">
   <si>
     <t>NGÀY</t>
   </si>
@@ -5336,6 +5336,12 @@
   </si>
   <si>
     <t>NGAY 16-10</t>
+  </si>
+  <si>
+    <t>kh ck shop 960k</t>
+  </si>
+  <si>
+    <t>kh ck shop 1965k</t>
   </si>
 </sst>
 </file>
@@ -5485,7 +5491,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -5508,6 +5514,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
@@ -5515,7 +5543,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5578,6 +5606,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19925,7 +19959,7 @@
     <col min="10" max="10" width="9.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" customWidth="1"/>
     <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" customWidth="1"/>
     <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -19989,8 +20023,8 @@
       <c r="P2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="56"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="20"/>
@@ -20016,7 +20050,7 @@
         <v>45</v>
       </c>
       <c r="I3" s="21">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I48" si="0">G3-H3</f>
         <v>3805</v>
       </c>
       <c r="J3" s="20" t="s">
@@ -20034,10 +20068,10 @@
       <c r="N3" s="20"/>
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
-      <c r="Q3" s="20">
-        <v>1</v>
-      </c>
-      <c r="R3" s="21">
+      <c r="Q3" s="54">
+        <v>1</v>
+      </c>
+      <c r="R3" s="57">
         <f>H3</f>
         <v>45</v>
       </c>
@@ -20066,7 +20100,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="21">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J4" s="20" t="s">
@@ -20082,10 +20116,10 @@
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
-      <c r="Q4" s="20">
-        <v>1</v>
-      </c>
-      <c r="R4" s="20"/>
+      <c r="Q4" s="54">
+        <v>1</v>
+      </c>
+      <c r="R4" s="56"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="20"/>
@@ -20111,7 +20145,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="21">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>920</v>
       </c>
       <c r="J5" s="20" t="s">
@@ -20127,10 +20161,10 @@
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
       <c r="P5" s="20"/>
-      <c r="Q5" s="20">
-        <v>1</v>
-      </c>
-      <c r="R5" s="20"/>
+      <c r="Q5" s="54">
+        <v>1</v>
+      </c>
+      <c r="R5" s="56"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="20"/>
@@ -20156,7 +20190,7 @@
         <v>25</v>
       </c>
       <c r="I6" s="21">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>1550</v>
       </c>
       <c r="J6" s="20" t="s">
@@ -20172,10 +20206,10 @@
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
       <c r="P6" s="20"/>
-      <c r="Q6" s="20">
-        <v>1</v>
-      </c>
-      <c r="R6" s="20"/>
+      <c r="Q6" s="54">
+        <v>1</v>
+      </c>
+      <c r="R6" s="56"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="20"/>
@@ -20201,7 +20235,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="21">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>760</v>
       </c>
       <c r="J7" s="20" t="s">
@@ -20217,10 +20251,10 @@
       <c r="N7" s="20"/>
       <c r="O7" s="20"/>
       <c r="P7" s="20"/>
-      <c r="Q7" s="20">
-        <v>1</v>
-      </c>
-      <c r="R7" s="20"/>
+      <c r="Q7" s="54">
+        <v>1</v>
+      </c>
+      <c r="R7" s="56"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="20"/>
@@ -20246,7 +20280,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="21">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>1080</v>
       </c>
       <c r="J8" s="20" t="s">
@@ -20262,10 +20296,10 @@
       <c r="N8" s="20"/>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
-      <c r="Q8" s="20">
-        <v>1</v>
-      </c>
-      <c r="R8" s="20"/>
+      <c r="Q8" s="54">
+        <v>1</v>
+      </c>
+      <c r="R8" s="56"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="20"/>
@@ -20291,7 +20325,7 @@
         <v>35</v>
       </c>
       <c r="I9" s="21">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>870</v>
       </c>
       <c r="J9" s="20" t="s">
@@ -20307,10 +20341,10 @@
       <c r="N9" s="20"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
-      <c r="Q9" s="20">
-        <v>1</v>
-      </c>
-      <c r="R9" s="20"/>
+      <c r="Q9" s="54">
+        <v>1</v>
+      </c>
+      <c r="R9" s="56"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="20"/>
@@ -20336,7 +20370,7 @@
         <v>35</v>
       </c>
       <c r="I10" s="21">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J10" s="20" t="s">
@@ -20352,11 +20386,11 @@
       <c r="N10" s="20"/>
       <c r="O10" s="20"/>
       <c r="P10" s="20"/>
-      <c r="Q10" s="20">
-        <v>1</v>
-      </c>
-      <c r="R10" s="21">
-        <f t="shared" ref="R10:R11" si="0">H10</f>
+      <c r="Q10" s="54">
+        <v>1</v>
+      </c>
+      <c r="R10" s="57">
+        <f t="shared" ref="R10:R11" si="1">H10</f>
         <v>35</v>
       </c>
     </row>
@@ -20384,7 +20418,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="21">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J11" s="20" t="s">
@@ -20400,11 +20434,11 @@
       <c r="N11" s="20"/>
       <c r="O11" s="20"/>
       <c r="P11" s="20"/>
-      <c r="Q11" s="20">
-        <v>1</v>
-      </c>
-      <c r="R11" s="21">
-        <f t="shared" si="0"/>
+      <c r="Q11" s="54">
+        <v>1</v>
+      </c>
+      <c r="R11" s="57">
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -20432,7 +20466,7 @@
         <v>30</v>
       </c>
       <c r="I12" s="21">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>430</v>
       </c>
       <c r="J12" s="20" t="s">
@@ -20448,10 +20482,10 @@
       <c r="N12" s="20"/>
       <c r="O12" s="20"/>
       <c r="P12" s="20"/>
-      <c r="Q12" s="20">
-        <v>1</v>
-      </c>
-      <c r="R12" s="20"/>
+      <c r="Q12" s="54">
+        <v>1</v>
+      </c>
+      <c r="R12" s="56"/>
     </row>
     <row r="13" spans="1:18" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>
@@ -20477,7 +20511,7 @@
         <v>30</v>
       </c>
       <c r="I13" s="25">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>140</v>
       </c>
       <c r="J13" s="24" t="s">
@@ -20495,10 +20529,10 @@
       <c r="N13" s="24"/>
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
-      <c r="Q13" s="24">
-        <v>1</v>
-      </c>
-      <c r="R13" s="24"/>
+      <c r="Q13" s="55">
+        <v>1</v>
+      </c>
+      <c r="R13" s="58"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
@@ -20524,7 +20558,7 @@
         <v>40</v>
       </c>
       <c r="I14" s="21">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="J14" s="20" t="s">
@@ -20540,10 +20574,10 @@
       <c r="N14" s="20"/>
       <c r="O14" s="20"/>
       <c r="P14" s="20"/>
-      <c r="Q14" s="20">
-        <v>1</v>
-      </c>
-      <c r="R14" s="20"/>
+      <c r="Q14" s="54">
+        <v>1</v>
+      </c>
+      <c r="R14" s="56"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
@@ -20569,7 +20603,7 @@
         <v>35</v>
       </c>
       <c r="I15" s="21">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J15" s="20" t="s">
@@ -20585,11 +20619,11 @@
       <c r="N15" s="20"/>
       <c r="O15" s="20"/>
       <c r="P15" s="20"/>
-      <c r="Q15" s="20">
-        <v>1</v>
-      </c>
-      <c r="R15" s="21">
-        <f t="shared" ref="R15:R19" si="1">H15</f>
+      <c r="Q15" s="54">
+        <v>1</v>
+      </c>
+      <c r="R15" s="57">
+        <f t="shared" ref="R15:R19" si="2">H15</f>
         <v>35</v>
       </c>
     </row>
@@ -20617,7 +20651,7 @@
         <v>35</v>
       </c>
       <c r="I16" s="21">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J16" s="20" t="s">
@@ -20633,11 +20667,11 @@
       <c r="N16" s="20"/>
       <c r="O16" s="20"/>
       <c r="P16" s="20"/>
-      <c r="Q16" s="20">
-        <v>1</v>
-      </c>
-      <c r="R16" s="21">
-        <f t="shared" si="1"/>
+      <c r="Q16" s="54">
+        <v>1</v>
+      </c>
+      <c r="R16" s="57">
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
@@ -20665,7 +20699,7 @@
         <v>35</v>
       </c>
       <c r="I17" s="21">
-        <f>G17-H17</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J17" s="20" t="s">
@@ -20681,11 +20715,11 @@
       <c r="N17" s="20"/>
       <c r="O17" s="20"/>
       <c r="P17" s="20"/>
-      <c r="Q17" s="20">
-        <v>1</v>
-      </c>
-      <c r="R17" s="21">
-        <f t="shared" si="1"/>
+      <c r="Q17" s="54">
+        <v>1</v>
+      </c>
+      <c r="R17" s="57">
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
@@ -20713,7 +20747,7 @@
         <v>20</v>
       </c>
       <c r="I18" s="25">
-        <f>G18-H18</f>
+        <f t="shared" si="0"/>
         <v>-20</v>
       </c>
       <c r="J18" s="24" t="s">
@@ -20731,11 +20765,11 @@
       <c r="N18" s="24"/>
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
-      <c r="Q18" s="24">
-        <v>1</v>
-      </c>
-      <c r="R18" s="25">
-        <f t="shared" si="1"/>
+      <c r="Q18" s="55">
+        <v>1</v>
+      </c>
+      <c r="R18" s="59">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
@@ -20763,7 +20797,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="21">
-        <f>G19-H19</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -20779,11 +20813,11 @@
       <c r="N19" s="20"/>
       <c r="O19" s="20"/>
       <c r="P19" s="20"/>
-      <c r="Q19" s="20">
-        <v>1</v>
-      </c>
-      <c r="R19" s="21">
-        <f t="shared" si="1"/>
+      <c r="Q19" s="54">
+        <v>1</v>
+      </c>
+      <c r="R19" s="57">
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
     </row>
@@ -20811,7 +20845,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="21">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="J20" s="20" t="s">
@@ -20827,10 +20861,10 @@
       <c r="N20" s="20"/>
       <c r="O20" s="20"/>
       <c r="P20" s="20"/>
-      <c r="Q20" s="20">
-        <v>1</v>
-      </c>
-      <c r="R20" s="20"/>
+      <c r="Q20" s="54">
+        <v>1</v>
+      </c>
+      <c r="R20" s="56"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="20"/>
@@ -20856,7 +20890,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="21">
-        <f>G21-H21</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -20872,10 +20906,10 @@
       <c r="N21" s="20"/>
       <c r="O21" s="20"/>
       <c r="P21" s="20"/>
-      <c r="Q21" s="20">
-        <v>1</v>
-      </c>
-      <c r="R21" s="21">
+      <c r="Q21" s="54">
+        <v>1</v>
+      </c>
+      <c r="R21" s="57">
         <f>H21</f>
         <v>30</v>
       </c>
@@ -20904,7 +20938,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="21">
-        <f>G22-H22</f>
+        <f t="shared" si="0"/>
         <v>690</v>
       </c>
       <c r="J22" s="20" t="s">
@@ -20920,10 +20954,10 @@
       <c r="N22" s="20"/>
       <c r="O22" s="20"/>
       <c r="P22" s="20"/>
-      <c r="Q22" s="20">
-        <v>1</v>
-      </c>
-      <c r="R22" s="20"/>
+      <c r="Q22" s="54">
+        <v>1</v>
+      </c>
+      <c r="R22" s="56"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
@@ -20949,7 +20983,7 @@
         <v>20</v>
       </c>
       <c r="I23" s="21">
-        <f>G23-H23</f>
+        <f t="shared" si="0"/>
         <v>1190</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -20965,10 +20999,10 @@
       <c r="N23" s="20"/>
       <c r="O23" s="20"/>
       <c r="P23" s="20"/>
-      <c r="Q23" s="20">
-        <v>1</v>
-      </c>
-      <c r="R23" s="20"/>
+      <c r="Q23" s="54">
+        <v>1</v>
+      </c>
+      <c r="R23" s="56"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="20"/>
@@ -20994,7 +21028,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="21">
-        <f>G24-H24</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J24" s="20" t="s">
@@ -21012,10 +21046,10 @@
       <c r="N24" s="20"/>
       <c r="O24" s="20"/>
       <c r="P24" s="20"/>
-      <c r="Q24" s="20">
-        <v>1</v>
-      </c>
-      <c r="R24" s="20"/>
+      <c r="Q24" s="54">
+        <v>1</v>
+      </c>
+      <c r="R24" s="56"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
@@ -21041,7 +21075,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="21">
-        <f>G25-H25</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -21059,10 +21093,10 @@
       <c r="N25" s="20"/>
       <c r="O25" s="20"/>
       <c r="P25" s="20"/>
-      <c r="Q25" s="20">
-        <v>1</v>
-      </c>
-      <c r="R25" s="20"/>
+      <c r="Q25" s="54">
+        <v>1</v>
+      </c>
+      <c r="R25" s="56"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
@@ -21088,7 +21122,7 @@
         <v>20</v>
       </c>
       <c r="I26" s="21">
-        <f>G26-H26</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="J26" s="20" t="s">
@@ -21104,10 +21138,10 @@
       <c r="N26" s="20"/>
       <c r="O26" s="20"/>
       <c r="P26" s="20"/>
-      <c r="Q26" s="20">
-        <v>1</v>
-      </c>
-      <c r="R26" s="20"/>
+      <c r="Q26" s="54">
+        <v>1</v>
+      </c>
+      <c r="R26" s="56"/>
     </row>
     <row r="27" spans="1:18" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="24"/>
@@ -21133,7 +21167,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="25">
-        <f>G27-H27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J27" s="24" t="s">
@@ -21151,10 +21185,10 @@
       <c r="N27" s="24"/>
       <c r="O27" s="24"/>
       <c r="P27" s="24"/>
-      <c r="Q27" s="24">
-        <v>1</v>
-      </c>
-      <c r="R27" s="24"/>
+      <c r="Q27" s="55">
+        <v>1</v>
+      </c>
+      <c r="R27" s="58"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="20"/>
@@ -21180,7 +21214,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="21">
-        <f>G28-H28</f>
+        <f t="shared" si="0"/>
         <v>1060</v>
       </c>
       <c r="J28" s="20" t="s">
@@ -21196,10 +21230,10 @@
       <c r="N28" s="20"/>
       <c r="O28" s="20"/>
       <c r="P28" s="20"/>
-      <c r="Q28" s="20">
-        <v>1</v>
-      </c>
-      <c r="R28" s="20"/>
+      <c r="Q28" s="54">
+        <v>1</v>
+      </c>
+      <c r="R28" s="56"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="20"/>
@@ -21225,7 +21259,7 @@
         <v>20</v>
       </c>
       <c r="I29" s="21">
-        <f>G29-H29</f>
+        <f t="shared" si="0"/>
         <v>930</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -21241,10 +21275,10 @@
       <c r="N29" s="20"/>
       <c r="O29" s="20"/>
       <c r="P29" s="20"/>
-      <c r="Q29" s="20">
-        <v>1</v>
-      </c>
-      <c r="R29" s="20"/>
+      <c r="Q29" s="54">
+        <v>1</v>
+      </c>
+      <c r="R29" s="56"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
@@ -21270,7 +21304,7 @@
         <v>70</v>
       </c>
       <c r="I30" s="21">
-        <f>G30-H30</f>
+        <f t="shared" si="0"/>
         <v>-70</v>
       </c>
       <c r="J30" s="20" t="s">
@@ -21286,11 +21320,11 @@
       <c r="N30" s="20"/>
       <c r="O30" s="20"/>
       <c r="P30" s="20"/>
-      <c r="Q30" s="20">
-        <v>1</v>
-      </c>
-      <c r="R30" s="21">
-        <f t="shared" ref="R30:R33" si="2">H30</f>
+      <c r="Q30" s="54">
+        <v>1</v>
+      </c>
+      <c r="R30" s="57">
+        <f t="shared" ref="R30:R33" si="3">H30</f>
         <v>70</v>
       </c>
     </row>
@@ -21318,7 +21352,7 @@
         <v>35</v>
       </c>
       <c r="I31" s="21">
-        <f>G31-H31</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J31" s="20" t="s">
@@ -21334,11 +21368,11 @@
       <c r="N31" s="20"/>
       <c r="O31" s="20"/>
       <c r="P31" s="20"/>
-      <c r="Q31" s="20">
-        <v>1</v>
-      </c>
-      <c r="R31" s="21">
-        <f t="shared" si="2"/>
+      <c r="Q31" s="54">
+        <v>1</v>
+      </c>
+      <c r="R31" s="57">
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
     </row>
@@ -21366,7 +21400,7 @@
         <v>35</v>
       </c>
       <c r="I32" s="21">
-        <f>G32-H32</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J32" s="20" t="s">
@@ -21382,11 +21416,11 @@
       <c r="N32" s="20"/>
       <c r="O32" s="20"/>
       <c r="P32" s="20"/>
-      <c r="Q32" s="20">
-        <v>1</v>
-      </c>
-      <c r="R32" s="21">
-        <f t="shared" si="2"/>
+      <c r="Q32" s="54">
+        <v>1</v>
+      </c>
+      <c r="R32" s="57">
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
     </row>
@@ -21414,7 +21448,7 @@
         <v>25</v>
       </c>
       <c r="I33" s="21">
-        <f>G33-H33</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J33" s="20" t="s">
@@ -21430,11 +21464,11 @@
       <c r="N33" s="20"/>
       <c r="O33" s="20"/>
       <c r="P33" s="20"/>
-      <c r="Q33" s="20">
-        <v>1</v>
-      </c>
-      <c r="R33" s="21">
-        <f t="shared" si="2"/>
+      <c r="Q33" s="54">
+        <v>1</v>
+      </c>
+      <c r="R33" s="57">
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
     </row>
@@ -21462,7 +21496,7 @@
         <v>30</v>
       </c>
       <c r="I34" s="21">
-        <f>G34-H34</f>
+        <f t="shared" si="0"/>
         <v>1480</v>
       </c>
       <c r="J34" s="20" t="s">
@@ -21478,10 +21512,10 @@
       <c r="N34" s="20"/>
       <c r="O34" s="20"/>
       <c r="P34" s="20"/>
-      <c r="Q34" s="20">
-        <v>1</v>
-      </c>
-      <c r="R34" s="20"/>
+      <c r="Q34" s="54">
+        <v>1</v>
+      </c>
+      <c r="R34" s="56"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="20"/>
@@ -21501,14 +21535,14 @@
         <v>218</v>
       </c>
       <c r="G35" s="21">
-        <v>1965</v>
+        <v>0</v>
       </c>
       <c r="H35" s="21">
         <v>35</v>
       </c>
       <c r="I35" s="21">
-        <f>G35-H35</f>
-        <v>1930</v>
+        <f t="shared" si="0"/>
+        <v>-35</v>
       </c>
       <c r="J35" s="20" t="s">
         <v>30</v>
@@ -21519,14 +21553,19 @@
       <c r="L35" s="20" t="s">
         <v>1642</v>
       </c>
-      <c r="M35" s="20"/>
+      <c r="M35" s="46" t="s">
+        <v>1751</v>
+      </c>
       <c r="N35" s="20"/>
       <c r="O35" s="20"/>
       <c r="P35" s="20"/>
-      <c r="Q35" s="20">
-        <v>1</v>
-      </c>
-      <c r="R35" s="20"/>
+      <c r="Q35" s="54">
+        <v>1</v>
+      </c>
+      <c r="R35" s="57">
+        <f t="shared" ref="R35" si="4">H35</f>
+        <v>35</v>
+      </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="20"/>
@@ -21552,7 +21591,7 @@
         <v>25</v>
       </c>
       <c r="I36" s="21">
-        <f>G36-H36</f>
+        <f t="shared" si="0"/>
         <v>760</v>
       </c>
       <c r="J36" s="20" t="s">
@@ -21568,10 +21607,10 @@
       <c r="N36" s="20"/>
       <c r="O36" s="20"/>
       <c r="P36" s="20"/>
-      <c r="Q36" s="20">
-        <v>1</v>
-      </c>
-      <c r="R36" s="20"/>
+      <c r="Q36" s="54">
+        <v>1</v>
+      </c>
+      <c r="R36" s="56"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="20"/>
@@ -21597,7 +21636,7 @@
         <v>30</v>
       </c>
       <c r="I37" s="21">
-        <f>G37-H37</f>
+        <f t="shared" si="0"/>
         <v>850</v>
       </c>
       <c r="J37" s="20" t="s">
@@ -21613,10 +21652,10 @@
       <c r="N37" s="20"/>
       <c r="O37" s="20"/>
       <c r="P37" s="20"/>
-      <c r="Q37" s="20">
-        <v>1</v>
-      </c>
-      <c r="R37" s="20"/>
+      <c r="Q37" s="54">
+        <v>1</v>
+      </c>
+      <c r="R37" s="56"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="20"/>
@@ -21642,7 +21681,7 @@
         <v>25</v>
       </c>
       <c r="I38" s="21">
-        <f>G38-H38</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J38" s="20" t="s">
@@ -21658,11 +21697,11 @@
       <c r="N38" s="20"/>
       <c r="O38" s="20"/>
       <c r="P38" s="20"/>
-      <c r="Q38" s="20">
-        <v>1</v>
-      </c>
-      <c r="R38" s="21">
-        <f t="shared" ref="R38:R39" si="3">H38</f>
+      <c r="Q38" s="54">
+        <v>1</v>
+      </c>
+      <c r="R38" s="57">
+        <f t="shared" ref="R38:R41" si="5">H38</f>
         <v>25</v>
       </c>
     </row>
@@ -21690,7 +21729,7 @@
         <v>25</v>
       </c>
       <c r="I39" s="21">
-        <f>G39-H39</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J39" s="20" t="s">
@@ -21706,11 +21745,11 @@
       <c r="N39" s="20"/>
       <c r="O39" s="20"/>
       <c r="P39" s="20"/>
-      <c r="Q39" s="20">
-        <v>1</v>
-      </c>
-      <c r="R39" s="21">
-        <f t="shared" si="3"/>
+      <c r="Q39" s="54">
+        <v>1</v>
+      </c>
+      <c r="R39" s="57">
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
     </row>
@@ -21738,7 +21777,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="21">
-        <f>G40-H40</f>
+        <f t="shared" si="0"/>
         <v>1080</v>
       </c>
       <c r="J40" s="20" t="s">
@@ -21754,10 +21793,10 @@
       <c r="N40" s="20"/>
       <c r="O40" s="20"/>
       <c r="P40" s="20"/>
-      <c r="Q40" s="20">
-        <v>1</v>
-      </c>
-      <c r="R40" s="20"/>
+      <c r="Q40" s="54">
+        <v>1</v>
+      </c>
+      <c r="R40" s="56"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="20"/>
@@ -21777,14 +21816,14 @@
         <v>7</v>
       </c>
       <c r="G41" s="21">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="H41" s="21">
         <v>30</v>
       </c>
       <c r="I41" s="21">
-        <f>G41-H41</f>
-        <v>930</v>
+        <f t="shared" si="0"/>
+        <v>-30</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>30</v>
@@ -21795,14 +21834,19 @@
       <c r="L41" s="20" t="s">
         <v>1642</v>
       </c>
-      <c r="M41" s="20"/>
+      <c r="M41" s="23" t="s">
+        <v>1750</v>
+      </c>
       <c r="N41" s="20"/>
       <c r="O41" s="20"/>
       <c r="P41" s="20"/>
-      <c r="Q41" s="20">
-        <v>1</v>
-      </c>
-      <c r="R41" s="20"/>
+      <c r="Q41" s="54">
+        <v>1</v>
+      </c>
+      <c r="R41" s="57">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="20"/>
@@ -21828,7 +21872,7 @@
         <v>25</v>
       </c>
       <c r="I42" s="21">
-        <f>G42-H42</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J42" s="20" t="s">
@@ -21844,10 +21888,10 @@
       <c r="N42" s="20"/>
       <c r="O42" s="20"/>
       <c r="P42" s="20"/>
-      <c r="Q42" s="20">
-        <v>1</v>
-      </c>
-      <c r="R42" s="20"/>
+      <c r="Q42" s="54">
+        <v>1</v>
+      </c>
+      <c r="R42" s="56"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="20"/>
@@ -21873,7 +21917,7 @@
         <v>25</v>
       </c>
       <c r="I43" s="21">
-        <f>G43-H43</f>
+        <f t="shared" si="0"/>
         <v>930</v>
       </c>
       <c r="J43" s="20" t="s">
@@ -21889,10 +21933,10 @@
       <c r="N43" s="20"/>
       <c r="O43" s="20"/>
       <c r="P43" s="20"/>
-      <c r="Q43" s="20">
-        <v>1</v>
-      </c>
-      <c r="R43" s="20"/>
+      <c r="Q43" s="54">
+        <v>1</v>
+      </c>
+      <c r="R43" s="56"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="20"/>
@@ -21918,7 +21962,7 @@
         <v>25</v>
       </c>
       <c r="I44" s="21">
-        <f>G44-H44</f>
+        <f t="shared" si="0"/>
         <v>1430</v>
       </c>
       <c r="J44" s="20" t="s">
@@ -21934,10 +21978,10 @@
       <c r="N44" s="20"/>
       <c r="O44" s="20"/>
       <c r="P44" s="20"/>
-      <c r="Q44" s="20">
-        <v>1</v>
-      </c>
-      <c r="R44" s="20"/>
+      <c r="Q44" s="54">
+        <v>1</v>
+      </c>
+      <c r="R44" s="56"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="20"/>
@@ -21963,7 +22007,7 @@
         <v>25</v>
       </c>
       <c r="I45" s="21">
-        <f>G45-H45</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J45" s="20" t="s">
@@ -21979,10 +22023,10 @@
       <c r="N45" s="20"/>
       <c r="O45" s="20"/>
       <c r="P45" s="20"/>
-      <c r="Q45" s="20">
-        <v>1</v>
-      </c>
-      <c r="R45" s="21">
+      <c r="Q45" s="54">
+        <v>1</v>
+      </c>
+      <c r="R45" s="57">
         <f>H45</f>
         <v>25</v>
       </c>
@@ -22011,7 +22055,7 @@
         <v>30</v>
       </c>
       <c r="I46" s="21">
-        <f>G46-H46</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J46" s="20" t="s">
@@ -22027,10 +22071,10 @@
       <c r="N46" s="20"/>
       <c r="O46" s="20"/>
       <c r="P46" s="20"/>
-      <c r="Q46" s="20">
-        <v>1</v>
-      </c>
-      <c r="R46" s="20"/>
+      <c r="Q46" s="54">
+        <v>1</v>
+      </c>
+      <c r="R46" s="56"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
@@ -22056,7 +22100,7 @@
         <v>60</v>
       </c>
       <c r="I47" s="21">
-        <f>G47-H47</f>
+        <f t="shared" si="0"/>
         <v>-60</v>
       </c>
       <c r="J47" s="20" t="s">
@@ -22072,11 +22116,11 @@
       <c r="N47" s="20"/>
       <c r="O47" s="20"/>
       <c r="P47" s="20"/>
-      <c r="Q47" s="20">
-        <v>1</v>
-      </c>
-      <c r="R47" s="21">
-        <f t="shared" ref="R47:R48" si="4">H47</f>
+      <c r="Q47" s="54">
+        <v>1</v>
+      </c>
+      <c r="R47" s="57">
+        <f t="shared" ref="R47:R48" si="6">H47</f>
         <v>60</v>
       </c>
     </row>
@@ -22104,7 +22148,7 @@
         <v>30</v>
       </c>
       <c r="I48" s="21">
-        <f>G48-H48</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J48" s="20" t="s">
@@ -22120,11 +22164,11 @@
       <c r="N48" s="20"/>
       <c r="O48" s="20"/>
       <c r="P48" s="20"/>
-      <c r="Q48" s="20">
-        <v>1</v>
-      </c>
-      <c r="R48" s="21">
-        <f t="shared" si="4"/>
+      <c r="Q48" s="54">
+        <v>1</v>
+      </c>
+      <c r="R48" s="57">
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
     </row>
@@ -22134,47 +22178,47 @@
         <v>35</v>
       </c>
       <c r="G50" s="9">
-        <f>SUBTOTAL(9,G3:G48)</f>
-        <v>29935</v>
+        <f t="shared" ref="G50:Q50" si="7">SUBTOTAL(9,G3:G48)</f>
+        <v>27010</v>
       </c>
       <c r="H50" s="9">
-        <f>SUBTOTAL(9,H3:H48)</f>
+        <f t="shared" si="7"/>
         <v>1390</v>
       </c>
       <c r="I50" s="9">
-        <f>SUBTOTAL(9,I3:I48)</f>
-        <v>28545</v>
+        <f t="shared" si="7"/>
+        <v>25620</v>
       </c>
       <c r="J50" s="9">
-        <f>SUBTOTAL(9,J3:J48)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K50" s="9">
-        <f>SUBTOTAL(9,K3:K48)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L50" s="9">
-        <f>SUBTOTAL(9,L3:L48)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M50" s="9">
-        <f>SUBTOTAL(9,M3:M48)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N50" s="9">
-        <f>SUBTOTAL(9,N3:N48)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O50" s="9">
-        <f>SUBTOTAL(9,O3:O48)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P50" s="9">
-        <f>SUBTOTAL(9,P3:P48)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q50" s="9">
-        <f>SUBTOTAL(9,Q3:Q48)</f>
+        <f t="shared" si="7"/>
         <v>46</v>
       </c>
     </row>
@@ -22221,7 +22265,7 @@
       </c>
       <c r="C53" s="52">
         <f>SUMIFS(I$3:I$48,B$3:B$48,A$52,L$3:L$48,A$53)</f>
-        <v>28545</v>
+        <v>25620</v>
       </c>
       <c r="D53" s="52"/>
       <c r="E53" s="12">
@@ -22310,7 +22354,7 @@
       </c>
       <c r="P55">
         <f>L74</f>
-        <v>9320</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -22319,7 +22363,7 @@
       </c>
       <c r="C56" s="51">
         <f>SUBTOTAL(9,C53:C55)</f>
-        <v>28545</v>
+        <v>25620</v>
       </c>
       <c r="D56" s="51"/>
       <c r="E56">
@@ -22334,7 +22378,7 @@
       </c>
       <c r="P56">
         <f>-C60</f>
-        <v>-28545</v>
+        <v>-25620</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -22375,7 +22419,7 @@
       </c>
       <c r="C60" s="50">
         <f>C56+C57+C58</f>
-        <v>28545</v>
+        <v>25620</v>
       </c>
       <c r="D60" s="50"/>
       <c r="E60" s="9" t="s">
@@ -22467,7 +22511,7 @@
       </c>
       <c r="L69">
         <f>SUMIFS(G$3:G$48,J$3:J$48,K$68)</f>
-        <v>9710</v>
+        <v>6785</v>
       </c>
       <c r="M69">
         <f>SUMIFS(Q$3:Q$48,J$3:J$48,K$68)-INT(COUNTIFS(J$3:J$48,K$68,M$3:M$48,"*gộp*")/2)</f>
@@ -22513,7 +22557,7 @@
     <row r="74" spans="11:13" x14ac:dyDescent="0.25">
       <c r="L74" s="16">
         <f>SUBTOTAL(9,L69:L73)</f>
-        <v>9320</v>
+        <v>6395</v>
       </c>
       <c r="M74" s="16">
         <f>M69</f>

--- a/data/Oct/InternalDailyReport_Oct.xlsx
+++ b/data/Oct/InternalDailyReport_Oct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4F8127-132A-41D5-9146-2828FEA5E497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF3F69D-1D50-4099-B8FD-C80BD259B311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="23" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="14-10" sheetId="35" r:id="rId13"/>
     <sheet name="15-10" sheetId="36" r:id="rId14"/>
     <sheet name="16-10" sheetId="37" r:id="rId15"/>
+    <sheet name="17-10" sheetId="38" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01-10'!$A$2:$P$53</definedName>
@@ -44,6 +45,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'14-10'!$A$2:$P$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'15-10'!$A$2:$P$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'16-10'!$A$2:$P$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'17-10'!$A$2:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -86,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5811" uniqueCount="1750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6115" uniqueCount="1831">
   <si>
     <t>NGÀY</t>
   </si>
@@ -5336,13 +5338,256 @@
   </si>
   <si>
     <t>NGAY 16-10</t>
+  </si>
+  <si>
+    <t>Thúy</t>
+  </si>
+  <si>
+    <t>HD067851</t>
+  </si>
+  <si>
+    <t>103/14B Trần Quang Diệu P Nhiêu Lộc</t>
+  </si>
+  <si>
+    <t>17-10-2026</t>
+  </si>
+  <si>
+    <t>Vương Huệ</t>
+  </si>
+  <si>
+    <t>HD067681</t>
+  </si>
+  <si>
+    <t>80 đg số 3 tân kiếng</t>
+  </si>
+  <si>
+    <t>HD067789</t>
+  </si>
+  <si>
+    <t>107 đường 4 khu tái định cư 680ha khu phố 11 linh xuân</t>
+  </si>
+  <si>
+    <t>huyền nguyễn</t>
+  </si>
+  <si>
+    <t>HD067857</t>
+  </si>
+  <si>
+    <t>243/44/12 tôn đản p15</t>
+  </si>
+  <si>
+    <t>HD067779</t>
+  </si>
+  <si>
+    <t>Như Lê</t>
+  </si>
+  <si>
+    <t>HD067675</t>
+  </si>
+  <si>
+    <t>95/70/2 lê văn lương phường tân hưng</t>
+  </si>
+  <si>
+    <t>Jessie Beauty</t>
+  </si>
+  <si>
+    <t>HD067697</t>
+  </si>
+  <si>
+    <t>Đặng Trinh ( phòng 103 )</t>
+  </si>
+  <si>
+    <t>HD067755</t>
+  </si>
+  <si>
+    <t>406/35 Cộng Hòa, Phường 13</t>
+  </si>
+  <si>
+    <t>Nguyen Hoang Ngoc Anh</t>
+  </si>
+  <si>
+    <t>HD067637</t>
+  </si>
+  <si>
+    <t>44/36 đông hưng thuận 6 phường tân hưng thuận</t>
+  </si>
+  <si>
+    <t>W2488</t>
+  </si>
+  <si>
+    <t>HD067898</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, Thới An</t>
+  </si>
+  <si>
+    <t>(Anna Hanh )</t>
+  </si>
+  <si>
+    <t>HD067782</t>
+  </si>
+  <si>
+    <t>188 Nguyễn Văn Công, P.3</t>
+  </si>
+  <si>
+    <t>Thảo Đoàn</t>
+  </si>
+  <si>
+    <t>HD067832</t>
+  </si>
+  <si>
+    <t>1041 Hồng Bàng, P.Phú Lâm</t>
+  </si>
+  <si>
+    <t>Lê Huyền Trang</t>
+  </si>
+  <si>
+    <t>HD067663</t>
+  </si>
+  <si>
+    <t>61 Đặng Minh Trứ phường Bảy Hiền</t>
+  </si>
+  <si>
+    <t>HD067735</t>
+  </si>
+  <si>
+    <t>Nhi Phan</t>
+  </si>
+  <si>
+    <t>HD067698</t>
+  </si>
+  <si>
+    <t>22 TÂN THỚI NHẤT 1B, Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>HD067687</t>
+  </si>
+  <si>
+    <t>Vy</t>
+  </si>
+  <si>
+    <t>HD067665</t>
+  </si>
+  <si>
+    <t>Số 6 hẻm 153 đường quốc lộ 13, phường 26</t>
+  </si>
+  <si>
+    <t>W2429</t>
+  </si>
+  <si>
+    <t>HD067615</t>
+  </si>
+  <si>
+    <t>WIND XPRESS ( vận chuyển Việt -&gt; thái ) Số 68 . Tân thới hiệp 14</t>
+  </si>
+  <si>
+    <t>Candy Kim</t>
+  </si>
+  <si>
+    <t>HD067682</t>
+  </si>
+  <si>
+    <t>31/23 đường làng tăng phú phường tăng nhơn phú a</t>
+  </si>
+  <si>
+    <t>Soya Su</t>
+  </si>
+  <si>
+    <t>HD067696</t>
+  </si>
+  <si>
+    <t>102 man thiện</t>
+  </si>
+  <si>
+    <t>Ngọc GiÀu</t>
+  </si>
+  <si>
+    <t>HD067791</t>
+  </si>
+  <si>
+    <t>207 trần văn kiểu phường bình phú</t>
+  </si>
+  <si>
+    <t>Hiếu Phan</t>
+  </si>
+  <si>
+    <t>HD067816</t>
+  </si>
+  <si>
+    <t>BS10A vinhomes grand park phường long bình</t>
+  </si>
+  <si>
+    <t>Linh Trần</t>
+  </si>
+  <si>
+    <t>HD067700</t>
+  </si>
+  <si>
+    <t>132 Bến Vân Đồn phường 6</t>
+  </si>
+  <si>
+    <t>Lữ Nhung Lữ Nhung</t>
+  </si>
+  <si>
+    <t>HD067826</t>
+  </si>
+  <si>
+    <t>28 Tân hương phường Phú Thọ Hòa</t>
+  </si>
+  <si>
+    <t>Thư</t>
+  </si>
+  <si>
+    <t>HD067829</t>
+  </si>
+  <si>
+    <t>76 trần đình xu</t>
+  </si>
+  <si>
+    <t>Bé Lan</t>
+  </si>
+  <si>
+    <t>HD067852</t>
+  </si>
+  <si>
+    <t>95 đường 59, P14</t>
+  </si>
+  <si>
+    <t>( Cẩm Giang) Kim Sarang</t>
+  </si>
+  <si>
+    <t>HD067864</t>
+  </si>
+  <si>
+    <t>Phong 1407 –Block B - Chung cư Opal Riverside, Đường Số 2, Phường Hiệp Bình</t>
+  </si>
+  <si>
+    <t>Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>417 Hậu Giang</t>
+  </si>
+  <si>
+    <t>Fangfang</t>
+  </si>
+  <si>
+    <t>A75/6B/2 Bạch Đằng,Phường 2</t>
+  </si>
+  <si>
+    <t>AT 17-10</t>
+  </si>
+  <si>
+    <t>đơn chuyển AT 17-10</t>
+  </si>
+  <si>
+    <t>NGAY 17-10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -5418,6 +5663,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -5515,7 +5766,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5578,6 +5829,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="12" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5934,7 +6189,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="str" cm="1">
-        <f t="array" aca="1" ref="A3:A16" ca="1">_xlfn.LET(
+        <f t="array" aca="1" ref="A3:A17" ca="1">_xlfn.LET(
     _xlpm.start,DATE(B1,--_xlfn.TEXTAFTER(A1," "),1),
     _xlpm.d,_xlfn._xlws.FILTER(
         _xlfn.SEQUENCE(DAY(EOMONTH(_xlpm.start,0)),,_xlpm.start),
@@ -6260,10 +6515,13 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
+      <c r="A17" s="3" t="str">
+        <f ca="1"/>
+        <v>17-10</v>
+      </c>
       <c r="B17" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C17" s="4">
         <f t="shared" ca="1" si="2"/>
@@ -6271,11 +6529,11 @@
       </c>
       <c r="D17" s="4" cm="1">
         <f t="array" aca="1" ref="D17" ca="1">IFERROR(SUM(COUNTIF(INDIRECT("'"&amp;A17&amp;"'!M3:M200"),{"*đơn trả*","*hàng tỉnh*"})),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -6493,7 +6751,7 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">SUBTOTAL(9,E3:E28)</f>
-        <v>600</v>
+        <v>629</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6510,7 +6768,7 @@
         ),
     0)
 )</f>
-        <v>2703</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -6519,7 +6777,7 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">-E29*2</f>
-        <v>-1200</v>
+        <v>-1258</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -6528,7 +6786,7 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">SUBTOTAL(9,E30:E31)</f>
-        <v>1503</v>
+        <v>1605</v>
       </c>
     </row>
   </sheetData>
@@ -20016,7 +20274,7 @@
         <v>45</v>
       </c>
       <c r="I3" s="21">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I48" si="0">G3-H3</f>
         <v>3805</v>
       </c>
       <c r="J3" s="20" t="s">
@@ -20066,7 +20324,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="21">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J4" s="20" t="s">
@@ -20111,7 +20369,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="21">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>920</v>
       </c>
       <c r="J5" s="20" t="s">
@@ -20156,7 +20414,7 @@
         <v>25</v>
       </c>
       <c r="I6" s="21">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>1550</v>
       </c>
       <c r="J6" s="20" t="s">
@@ -20201,7 +20459,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="21">
-        <f>G7-H7</f>
+        <f t="shared" si="0"/>
         <v>760</v>
       </c>
       <c r="J7" s="20" t="s">
@@ -20246,7 +20504,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="21">
-        <f>G8-H8</f>
+        <f t="shared" si="0"/>
         <v>1080</v>
       </c>
       <c r="J8" s="20" t="s">
@@ -20291,7 +20549,7 @@
         <v>35</v>
       </c>
       <c r="I9" s="21">
-        <f>G9-H9</f>
+        <f t="shared" si="0"/>
         <v>870</v>
       </c>
       <c r="J9" s="20" t="s">
@@ -20336,7 +20594,7 @@
         <v>35</v>
       </c>
       <c r="I10" s="21">
-        <f>G10-H10</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J10" s="20" t="s">
@@ -20356,7 +20614,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="21">
-        <f t="shared" ref="R10:R11" si="0">H10</f>
+        <f t="shared" ref="R10:R11" si="1">H10</f>
         <v>35</v>
       </c>
     </row>
@@ -20384,7 +20642,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="21">
-        <f>G11-H11</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J11" s="20" t="s">
@@ -20404,7 +20662,7 @@
         <v>1</v>
       </c>
       <c r="R11" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -20432,7 +20690,7 @@
         <v>30</v>
       </c>
       <c r="I12" s="21">
-        <f>G12-H12</f>
+        <f t="shared" si="0"/>
         <v>430</v>
       </c>
       <c r="J12" s="20" t="s">
@@ -20477,7 +20735,7 @@
         <v>30</v>
       </c>
       <c r="I13" s="25">
-        <f>G13-H13</f>
+        <f t="shared" si="0"/>
         <v>140</v>
       </c>
       <c r="J13" s="24" t="s">
@@ -20524,7 +20782,7 @@
         <v>40</v>
       </c>
       <c r="I14" s="21">
-        <f>G14-H14</f>
+        <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="J14" s="20" t="s">
@@ -20569,7 +20827,7 @@
         <v>35</v>
       </c>
       <c r="I15" s="21">
-        <f>G15-H15</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J15" s="20" t="s">
@@ -20589,7 +20847,7 @@
         <v>1</v>
       </c>
       <c r="R15" s="21">
-        <f t="shared" ref="R15:R19" si="1">H15</f>
+        <f t="shared" ref="R15:R19" si="2">H15</f>
         <v>35</v>
       </c>
     </row>
@@ -20617,7 +20875,7 @@
         <v>35</v>
       </c>
       <c r="I16" s="21">
-        <f>G16-H16</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J16" s="20" t="s">
@@ -20637,7 +20895,7 @@
         <v>1</v>
       </c>
       <c r="R16" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
@@ -20665,7 +20923,7 @@
         <v>35</v>
       </c>
       <c r="I17" s="21">
-        <f>G17-H17</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J17" s="20" t="s">
@@ -20685,7 +20943,7 @@
         <v>1</v>
       </c>
       <c r="R17" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
@@ -20713,7 +20971,7 @@
         <v>20</v>
       </c>
       <c r="I18" s="25">
-        <f>G18-H18</f>
+        <f t="shared" si="0"/>
         <v>-20</v>
       </c>
       <c r="J18" s="24" t="s">
@@ -20735,7 +20993,7 @@
         <v>1</v>
       </c>
       <c r="R18" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
     </row>
@@ -20763,7 +21021,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="21">
-        <f>G19-H19</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -20783,7 +21041,7 @@
         <v>1</v>
       </c>
       <c r="R19" s="21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
     </row>
@@ -20811,7 +21069,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="21">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="J20" s="20" t="s">
@@ -20856,7 +21114,7 @@
         <v>30</v>
       </c>
       <c r="I21" s="21">
-        <f>G21-H21</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -20904,7 +21162,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="21">
-        <f>G22-H22</f>
+        <f t="shared" si="0"/>
         <v>690</v>
       </c>
       <c r="J22" s="20" t="s">
@@ -20949,7 +21207,7 @@
         <v>20</v>
       </c>
       <c r="I23" s="21">
-        <f>G23-H23</f>
+        <f t="shared" si="0"/>
         <v>1190</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -20988,14 +21246,14 @@
         <v>2</v>
       </c>
       <c r="G24" s="21">
-        <v>920</v>
+        <v>720</v>
       </c>
       <c r="H24" s="21">
         <v>30</v>
       </c>
       <c r="I24" s="21">
-        <f>G24-H24</f>
-        <v>890</v>
+        <f t="shared" si="0"/>
+        <v>690</v>
       </c>
       <c r="J24" s="20" t="s">
         <v>31</v>
@@ -21041,7 +21299,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="21">
-        <f>G25-H25</f>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -21088,7 +21346,7 @@
         <v>20</v>
       </c>
       <c r="I26" s="21">
-        <f>G26-H26</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="J26" s="20" t="s">
@@ -21133,7 +21391,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="25">
-        <f>G27-H27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J27" s="24" t="s">
@@ -21180,7 +21438,7 @@
         <v>30</v>
       </c>
       <c r="I28" s="21">
-        <f>G28-H28</f>
+        <f t="shared" si="0"/>
         <v>1060</v>
       </c>
       <c r="J28" s="20" t="s">
@@ -21225,7 +21483,7 @@
         <v>20</v>
       </c>
       <c r="I29" s="21">
-        <f>G29-H29</f>
+        <f t="shared" si="0"/>
         <v>930</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -21270,7 +21528,7 @@
         <v>70</v>
       </c>
       <c r="I30" s="21">
-        <f>G30-H30</f>
+        <f t="shared" si="0"/>
         <v>-70</v>
       </c>
       <c r="J30" s="20" t="s">
@@ -21290,7 +21548,7 @@
         <v>1</v>
       </c>
       <c r="R30" s="21">
-        <f t="shared" ref="R30:R33" si="2">H30</f>
+        <f t="shared" ref="R30:R33" si="3">H30</f>
         <v>70</v>
       </c>
     </row>
@@ -21318,7 +21576,7 @@
         <v>35</v>
       </c>
       <c r="I31" s="21">
-        <f>G31-H31</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J31" s="20" t="s">
@@ -21338,7 +21596,7 @@
         <v>1</v>
       </c>
       <c r="R31" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
     </row>
@@ -21366,7 +21624,7 @@
         <v>35</v>
       </c>
       <c r="I32" s="21">
-        <f>G32-H32</f>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J32" s="20" t="s">
@@ -21386,7 +21644,7 @@
         <v>1</v>
       </c>
       <c r="R32" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
     </row>
@@ -21414,7 +21672,7 @@
         <v>25</v>
       </c>
       <c r="I33" s="21">
-        <f>G33-H33</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J33" s="20" t="s">
@@ -21434,7 +21692,7 @@
         <v>1</v>
       </c>
       <c r="R33" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
     </row>
@@ -21462,7 +21720,7 @@
         <v>30</v>
       </c>
       <c r="I34" s="21">
-        <f>G34-H34</f>
+        <f t="shared" si="0"/>
         <v>1480</v>
       </c>
       <c r="J34" s="20" t="s">
@@ -21507,7 +21765,7 @@
         <v>35</v>
       </c>
       <c r="I35" s="21">
-        <f>G35-H35</f>
+        <f t="shared" si="0"/>
         <v>1930</v>
       </c>
       <c r="J35" s="20" t="s">
@@ -21552,7 +21810,7 @@
         <v>25</v>
       </c>
       <c r="I36" s="21">
-        <f>G36-H36</f>
+        <f t="shared" si="0"/>
         <v>760</v>
       </c>
       <c r="J36" s="20" t="s">
@@ -21597,7 +21855,7 @@
         <v>30</v>
       </c>
       <c r="I37" s="21">
-        <f>G37-H37</f>
+        <f t="shared" si="0"/>
         <v>850</v>
       </c>
       <c r="J37" s="20" t="s">
@@ -21642,7 +21900,7 @@
         <v>25</v>
       </c>
       <c r="I38" s="21">
-        <f>G38-H38</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J38" s="20" t="s">
@@ -21662,7 +21920,7 @@
         <v>1</v>
       </c>
       <c r="R38" s="21">
-        <f t="shared" ref="R38:R39" si="3">H38</f>
+        <f t="shared" ref="R38:R39" si="4">H38</f>
         <v>25</v>
       </c>
     </row>
@@ -21690,7 +21948,7 @@
         <v>25</v>
       </c>
       <c r="I39" s="21">
-        <f>G39-H39</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J39" s="20" t="s">
@@ -21710,7 +21968,7 @@
         <v>1</v>
       </c>
       <c r="R39" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
     </row>
@@ -21738,7 +21996,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="21">
-        <f>G40-H40</f>
+        <f t="shared" si="0"/>
         <v>1080</v>
       </c>
       <c r="J40" s="20" t="s">
@@ -21783,7 +22041,7 @@
         <v>30</v>
       </c>
       <c r="I41" s="21">
-        <f>G41-H41</f>
+        <f t="shared" si="0"/>
         <v>930</v>
       </c>
       <c r="J41" s="20" t="s">
@@ -21828,7 +22086,7 @@
         <v>25</v>
       </c>
       <c r="I42" s="21">
-        <f>G42-H42</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J42" s="20" t="s">
@@ -21873,7 +22131,7 @@
         <v>25</v>
       </c>
       <c r="I43" s="21">
-        <f>G43-H43</f>
+        <f t="shared" si="0"/>
         <v>930</v>
       </c>
       <c r="J43" s="20" t="s">
@@ -21918,7 +22176,7 @@
         <v>25</v>
       </c>
       <c r="I44" s="21">
-        <f>G44-H44</f>
+        <f t="shared" si="0"/>
         <v>1430</v>
       </c>
       <c r="J44" s="20" t="s">
@@ -21963,7 +22221,7 @@
         <v>25</v>
       </c>
       <c r="I45" s="21">
-        <f>G45-H45</f>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J45" s="20" t="s">
@@ -22011,7 +22269,7 @@
         <v>30</v>
       </c>
       <c r="I46" s="21">
-        <f>G46-H46</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J46" s="20" t="s">
@@ -22056,7 +22314,7 @@
         <v>60</v>
       </c>
       <c r="I47" s="21">
-        <f>G47-H47</f>
+        <f t="shared" si="0"/>
         <v>-60</v>
       </c>
       <c r="J47" s="20" t="s">
@@ -22076,7 +22334,7 @@
         <v>1</v>
       </c>
       <c r="R47" s="21">
-        <f t="shared" ref="R47:R48" si="4">H47</f>
+        <f t="shared" ref="R47:R48" si="5">H47</f>
         <v>60</v>
       </c>
     </row>
@@ -22104,7 +22362,7 @@
         <v>30</v>
       </c>
       <c r="I48" s="21">
-        <f>G48-H48</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J48" s="20" t="s">
@@ -22124,7 +22382,7 @@
         <v>1</v>
       </c>
       <c r="R48" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
     </row>
@@ -22134,47 +22392,47 @@
         <v>35</v>
       </c>
       <c r="G50" s="9">
-        <f>SUBTOTAL(9,G3:G48)</f>
-        <v>29935</v>
+        <f t="shared" ref="G50:Q50" si="6">SUBTOTAL(9,G3:G48)</f>
+        <v>29735</v>
       </c>
       <c r="H50" s="9">
-        <f>SUBTOTAL(9,H3:H48)</f>
+        <f t="shared" si="6"/>
         <v>1390</v>
       </c>
       <c r="I50" s="9">
-        <f>SUBTOTAL(9,I3:I48)</f>
-        <v>28545</v>
+        <f t="shared" si="6"/>
+        <v>28345</v>
       </c>
       <c r="J50" s="9">
-        <f>SUBTOTAL(9,J3:J48)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K50" s="9">
-        <f>SUBTOTAL(9,K3:K48)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L50" s="9">
-        <f>SUBTOTAL(9,L3:L48)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M50" s="9">
-        <f>SUBTOTAL(9,M3:M48)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N50" s="9">
-        <f>SUBTOTAL(9,N3:N48)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O50" s="9">
-        <f>SUBTOTAL(9,O3:O48)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P50" s="9">
-        <f>SUBTOTAL(9,P3:P48)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q50" s="9">
-        <f>SUBTOTAL(9,Q3:Q48)</f>
+        <f t="shared" si="6"/>
         <v>46</v>
       </c>
     </row>
@@ -22221,7 +22479,7 @@
       </c>
       <c r="C53" s="52">
         <f>SUMIFS(I$3:I$48,B$3:B$48,A$52,L$3:L$48,A$53)</f>
-        <v>28545</v>
+        <v>28345</v>
       </c>
       <c r="D53" s="52"/>
       <c r="E53" s="12">
@@ -22240,7 +22498,7 @@
       </c>
       <c r="L53">
         <f>SUMIFS(G$3:G$48,J$3:J$48,K$52)</f>
-        <v>7455</v>
+        <v>7255</v>
       </c>
       <c r="M53">
         <f>SUMIFS(Q$3:Q$48,J$3:J$48,K$52)-INT(COUNTIFS(J$3:J$48,K$52,M$3:M$48,"*gộp*")/2)</f>
@@ -22251,7 +22509,7 @@
       </c>
       <c r="P53">
         <f>L58</f>
-        <v>7010</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -22319,7 +22577,7 @@
       </c>
       <c r="C56" s="51">
         <f>SUBTOTAL(9,C53:C55)</f>
-        <v>28545</v>
+        <v>28345</v>
       </c>
       <c r="D56" s="51"/>
       <c r="E56">
@@ -22334,7 +22592,7 @@
       </c>
       <c r="P56">
         <f>-C60</f>
-        <v>-28545</v>
+        <v>-28345</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -22362,7 +22620,7 @@
       <c r="D58" s="49"/>
       <c r="L58" s="16">
         <f>SUBTOTAL(9,L53:L57)</f>
-        <v>7010</v>
+        <v>6810</v>
       </c>
       <c r="M58" s="16">
         <f>M53</f>
@@ -22375,7 +22633,7 @@
       </c>
       <c r="C60" s="50">
         <f>C56+C57+C58</f>
-        <v>28545</v>
+        <v>28345</v>
       </c>
       <c r="D60" s="50"/>
       <c r="E60" s="9" t="s">
@@ -22538,6 +22796,1941 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A973269-8F7C-4EEB-91DD-E47E3377A1CB}">
+  <dimension ref="A1:R60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="5" max="5" width="71.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="17" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>1782</v>
+      </c>
+      <c r="F3" s="21">
+        <v>6</v>
+      </c>
+      <c r="G3" s="21">
+        <v>955</v>
+      </c>
+      <c r="H3" s="21">
+        <v>25</v>
+      </c>
+      <c r="I3" s="21">
+        <f>G3-H3</f>
+        <v>930</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>1784</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>1785</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" s="21">
+        <v>945</v>
+      </c>
+      <c r="H4" s="21">
+        <v>25</v>
+      </c>
+      <c r="I4" s="21">
+        <f>G4-H4</f>
+        <v>920</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1790</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="21">
+        <v>1750</v>
+      </c>
+      <c r="H5" s="21">
+        <v>30</v>
+      </c>
+      <c r="I5" s="21">
+        <f>G5-H5</f>
+        <v>1720</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F6" s="21">
+        <v>6</v>
+      </c>
+      <c r="G6" s="21">
+        <v>855</v>
+      </c>
+      <c r="H6" s="21">
+        <v>25</v>
+      </c>
+      <c r="I6" s="21">
+        <f>G6-H6</f>
+        <v>830</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>1813</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>1814</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" s="21">
+        <v>645</v>
+      </c>
+      <c r="H7" s="21">
+        <v>25</v>
+      </c>
+      <c r="I7" s="21">
+        <f>G7-H7</f>
+        <v>620</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F8" s="21">
+        <v>6</v>
+      </c>
+      <c r="G8" s="21">
+        <v>600</v>
+      </c>
+      <c r="H8" s="21">
+        <v>30</v>
+      </c>
+      <c r="I8" s="21">
+        <f>G8-H8</f>
+        <v>570</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="21">
+        <v>13880</v>
+      </c>
+      <c r="H9" s="21">
+        <v>80</v>
+      </c>
+      <c r="I9" s="21">
+        <f>G9-H9</f>
+        <v>13800</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="57" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="54"/>
+      <c r="B10" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D10" s="54" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E10" s="54" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F10" s="55">
+        <v>5</v>
+      </c>
+      <c r="G10" s="55">
+        <v>785</v>
+      </c>
+      <c r="H10" s="55">
+        <v>25</v>
+      </c>
+      <c r="I10" s="55">
+        <f>G10-H10</f>
+        <v>760</v>
+      </c>
+      <c r="J10" s="54" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K10" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="54" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M10" s="54" t="s">
+        <v>1829</v>
+      </c>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="45" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>1757</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="21">
+        <v>860</v>
+      </c>
+      <c r="H11" s="21">
+        <v>30</v>
+      </c>
+      <c r="I11" s="21">
+        <f>G11-H11</f>
+        <v>830</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="21">
+        <v>955</v>
+      </c>
+      <c r="H12" s="21">
+        <v>25</v>
+      </c>
+      <c r="I12" s="21">
+        <f>G12-H12</f>
+        <v>930</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>1773</v>
+      </c>
+      <c r="F13" s="21">
+        <v>12</v>
+      </c>
+      <c r="G13" s="21">
+        <v>790</v>
+      </c>
+      <c r="H13" s="21">
+        <v>30</v>
+      </c>
+      <c r="I13" s="21">
+        <f>G13-H13</f>
+        <v>760</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F14" s="21">
+        <v>12</v>
+      </c>
+      <c r="G14" s="21">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21">
+        <f>G14-H14</f>
+        <v>-30</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+      <c r="R14" s="8">
+        <f>H14</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="21">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21">
+        <v>25</v>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+      <c r="R15" s="8">
+        <f>H15</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F16" s="21">
+        <v>9</v>
+      </c>
+      <c r="G16" s="21">
+        <v>1110</v>
+      </c>
+      <c r="H16" s="21">
+        <v>30</v>
+      </c>
+      <c r="I16" s="21">
+        <f>G16-H16</f>
+        <v>1080</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F17" s="21">
+        <v>12</v>
+      </c>
+      <c r="G17" s="21">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21">
+        <v>30</v>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20">
+        <v>1</v>
+      </c>
+      <c r="R17" s="8">
+        <f t="shared" ref="R17:R19" si="0">H17</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>1792</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="21">
+        <v>0</v>
+      </c>
+      <c r="H18" s="21">
+        <v>20</v>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v>-20</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20">
+        <v>1</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F19" s="21">
+        <v>12</v>
+      </c>
+      <c r="G19" s="21">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21">
+        <v>30</v>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20">
+        <v>1</v>
+      </c>
+      <c r="R19" s="8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>1798</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F20" s="21">
+        <v>9</v>
+      </c>
+      <c r="G20" s="21">
+        <v>820</v>
+      </c>
+      <c r="H20" s="21">
+        <v>30</v>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v>790</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F21" s="21">
+        <v>9</v>
+      </c>
+      <c r="G21" s="21">
+        <v>900</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30</v>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v>870</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>1808</v>
+      </c>
+      <c r="F22" s="21">
+        <v>9</v>
+      </c>
+      <c r="G22" s="21">
+        <v>1110</v>
+      </c>
+      <c r="H22" s="21">
+        <v>30</v>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v>1080</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>1819</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="21">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21">
+        <v>25</v>
+      </c>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20">
+        <v>1</v>
+      </c>
+      <c r="R23" s="8">
+        <f>H23</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>1822</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="21">
+        <v>1090</v>
+      </c>
+      <c r="H24" s="21">
+        <v>30</v>
+      </c>
+      <c r="I24" s="21">
+        <f>G24-H24</f>
+        <v>1060</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>1752</v>
+      </c>
+      <c r="F25" s="21">
+        <v>3</v>
+      </c>
+      <c r="G25" s="21">
+        <v>855</v>
+      </c>
+      <c r="H25" s="21">
+        <v>25</v>
+      </c>
+      <c r="I25" s="21">
+        <f>G25-H25</f>
+        <v>830</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F26" s="21">
+        <v>7</v>
+      </c>
+      <c r="G26" s="21">
+        <v>920</v>
+      </c>
+      <c r="H26" s="21">
+        <v>30</v>
+      </c>
+      <c r="I26" s="21">
+        <f>G26-H26</f>
+        <v>890</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F27" s="21">
+        <v>4</v>
+      </c>
+      <c r="G27" s="21">
+        <v>1035</v>
+      </c>
+      <c r="H27" s="21">
+        <v>25</v>
+      </c>
+      <c r="I27" s="21">
+        <f>G27-H27</f>
+        <v>1010</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F28" s="21">
+        <v>7</v>
+      </c>
+      <c r="G28" s="21">
+        <v>960</v>
+      </c>
+      <c r="H28" s="21">
+        <v>30</v>
+      </c>
+      <c r="I28" s="21">
+        <f>G28-H28</f>
+        <v>930</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="21">
+        <v>785</v>
+      </c>
+      <c r="H29" s="21">
+        <v>25</v>
+      </c>
+      <c r="I29" s="21">
+        <f>G29-H29</f>
+        <v>760</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>1770</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G30" s="21">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21">
+        <v>25</v>
+      </c>
+      <c r="I30" s="21">
+        <f>G30-H30</f>
+        <v>-25</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20">
+        <v>1</v>
+      </c>
+      <c r="R30" s="8">
+        <f>H30</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>1810</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>1811</v>
+      </c>
+      <c r="F31" s="21">
+        <v>4</v>
+      </c>
+      <c r="G31" s="21">
+        <v>785</v>
+      </c>
+      <c r="H31" s="21">
+        <v>25</v>
+      </c>
+      <c r="I31" s="21">
+        <f>G31-H31</f>
+        <v>760</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>1816</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>1817</v>
+      </c>
+      <c r="F32" s="21">
+        <v>1</v>
+      </c>
+      <c r="G32" s="21">
+        <v>665</v>
+      </c>
+      <c r="H32" s="21">
+        <v>25</v>
+      </c>
+      <c r="I32" s="21">
+        <f>G32-H32</f>
+        <v>640</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" s="21">
+        <v>960</v>
+      </c>
+      <c r="H33" s="21">
+        <v>30</v>
+      </c>
+      <c r="I33" s="21">
+        <f>G33-H33</f>
+        <v>930</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>1753</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>1716</v>
+      </c>
+      <c r="F34" s="27">
+        <v>1</v>
+      </c>
+      <c r="G34" s="27">
+        <v>955</v>
+      </c>
+      <c r="H34" s="27">
+        <v>25</v>
+      </c>
+      <c r="I34" s="27">
+        <f>G34-H34</f>
+        <v>930</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M34" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="N34" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="O34" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="P34" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q34" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D36" s="9">
+        <f>COUNTA(D3:D34)</f>
+        <v>29</v>
+      </c>
+      <c r="G36" s="9">
+        <f t="shared" ref="G36:Q36" si="1">SUBTOTAL(9,G3:G34)</f>
+        <v>35970</v>
+      </c>
+      <c r="H36" s="9">
+        <f t="shared" si="1"/>
+        <v>925</v>
+      </c>
+      <c r="I36" s="9">
+        <f t="shared" si="1"/>
+        <v>35045</v>
+      </c>
+      <c r="J36" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="9">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H37">
+        <f>-6*17</f>
+        <v>-102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" s="51"/>
+      <c r="E38" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="H38">
+        <f>-2*25</f>
+        <v>-50</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="O38" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" s="52">
+        <f>SUMIFS(I$3:I$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+        <v>33355</v>
+      </c>
+      <c r="D39" s="52"/>
+      <c r="E39" s="12">
+        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,L$3:L$34,A$39)</f>
+        <v>30</v>
+      </c>
+      <c r="F39" t="s">
+        <v>194</v>
+      </c>
+      <c r="K39" t="s">
+        <v>195</v>
+      </c>
+      <c r="L39">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$38)</f>
+        <v>6965</v>
+      </c>
+      <c r="M39">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-INT(COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+      <c r="O39" t="s">
+        <v>30</v>
+      </c>
+      <c r="P39">
+        <f>L44</f>
+        <v>5070</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B40" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" s="53">
+        <v>0</v>
+      </c>
+      <c r="D40" s="53"/>
+      <c r="K40" t="s">
+        <v>197</v>
+      </c>
+      <c r="L40">
+        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$38)+M40*5</f>
+        <v>-195</v>
+      </c>
+      <c r="M40">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$38)-INT(COUNTIFS(J$3:J$34,K$38,M$3:M$34,"*gộp*")/2)</f>
+        <v>9</v>
+      </c>
+      <c r="O40" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40">
+        <f>L52</f>
+        <v>7252</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" s="53">
+        <f>-SUMIFS(I$3:I$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
+        <v>-930</v>
+      </c>
+      <c r="D41" s="53"/>
+      <c r="E41" s="13">
+        <f>SUMIFS(Q$3:Q$34,B$3:B$34,A$38,P$3:P$34,"xx",N$3:N$34,"x")</f>
+        <v>1</v>
+      </c>
+      <c r="K41" t="s">
+        <v>200</v>
+      </c>
+      <c r="L41">
+        <f>-M41*2</f>
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f>COUNTIFS(K$3:K$34,K$38,L$3:L$34,A$39)-(COUNTIFS(K$3:K$34,K$38,M$3:M$34,"*gộp*")/2)-COUNTIFS(K$3:K$34,K$38,M$3:M$34,"*đơn trả*")-COUNTIFS(K$3:K$34,K$38,M$3:M$34,"*hàng tỉnh*")</f>
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>1828</v>
+      </c>
+      <c r="P41">
+        <f>L60</f>
+        <v>20263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B42" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" s="51">
+        <f>SUBTOTAL(9,C39:C41)</f>
+        <v>32425</v>
+      </c>
+      <c r="D42" s="51"/>
+      <c r="E42">
+        <f>E39</f>
+        <v>30</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="L42" s="28">
+        <v>-1700</v>
+      </c>
+      <c r="M42" s="28" t="s">
+        <v>1388</v>
+      </c>
+      <c r="O42" t="s">
+        <v>203</v>
+      </c>
+      <c r="P42">
+        <f>-C46</f>
+        <v>-32425</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B43" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="K43" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="O43" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P43" s="10">
+        <f>SUBTOTAL(9,P39:P42)</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B44" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="L44" s="16">
+        <f>SUBTOTAL(9,L39:L43)</f>
+        <v>5070</v>
+      </c>
+      <c r="M44" s="16">
+        <f>M39</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B46" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C46" s="50">
+        <f>C42+C43+C44</f>
+        <v>32425</v>
+      </c>
+      <c r="D46" s="50"/>
+      <c r="E46" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K47" t="s">
+        <v>195</v>
+      </c>
+      <c r="L47">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$46)</f>
+        <v>7635</v>
+      </c>
+      <c r="M47">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)-INT(COUNTIFS(J$3:J$34,K$46,M$3:M$34,"*gộp*")/2)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="K48" t="s">
+        <v>197</v>
+      </c>
+      <c r="L48">
+        <f>-SUMIFS(H$3:H$34,J$3:J$34,K$46)+M48*5</f>
+        <v>-325</v>
+      </c>
+      <c r="M48">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$46)-INT(COUNTIFS(J$3:J$34,K$46,M$3:M$34,"*gộp*")/2)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K49" t="s">
+        <v>200</v>
+      </c>
+      <c r="L49">
+        <f>-M49*2</f>
+        <v>-58</v>
+      </c>
+      <c r="M49">
+        <f>COUNTIFS(K$3:K$34,K$46,L$3:L$34,A$39)-(COUNTIFS(K$3:K$34,K$46,M$3:M$34,"*gộp*")/2)-COUNTIFS(K$3:K$34,K$46,M$3:M$34,"*đơn trả*")-COUNTIFS(K$3:K$34,K$46,M$3:M$34,"*hàng tỉnh*")</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K50" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K51" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="52" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L52" s="16">
+        <f>SUBTOTAL(9,L47:L51)</f>
+        <v>7252</v>
+      </c>
+      <c r="M52" s="16">
+        <f>M47</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K54" s="11" t="s">
+        <v>1828</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K55" t="s">
+        <v>195</v>
+      </c>
+      <c r="L55">
+        <f>SUMIFS(G$3:G$34,J$3:J$34,K$54)</f>
+        <v>20415</v>
+      </c>
+      <c r="M55">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)-INT(COUNTIFS(J$3:J$34,K$54,M$3:M$34,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K56" t="s">
+        <v>197</v>
+      </c>
+      <c r="L56">
+        <f>SUM(H37:H38)</f>
+        <v>-152</v>
+      </c>
+      <c r="M56">
+        <f>SUMIFS(Q$3:Q$34,J$3:J$34,K$54)-INT(COUNTIFS(J$3:J$34,K$54,M$3:M$34,"*gộp*")/2)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K58" s="14" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K59" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="L60" s="16">
+        <f>SUBTOTAL(9,L55:L59)</f>
+        <v>20263</v>
+      </c>
+      <c r="M60" s="16">
+        <f>M55</f>
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P34" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P34">
+      <sortCondition ref="J2:J34"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="8">
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
 </file>
 
